--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} uniones bridadas del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica moderada.</t>
+          <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} unión(es) bridada(s) del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica moderada.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento de los elementos de ajuste de acero al carbono (espárragos y tuercas) en las {cantidad} uniones bridadas afectadas, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar el mantenimiento de los elementos de ajuste de acero al carbono (espárragos y tuercas) en {cantidad} unión(es) bridada(s) afectada(s), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>cantidad_elementos=sus</t>
+          <t>cantidad_elementos=sus; cantidad=1</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} uniones bridadas del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica {severidad}.</t>
+          <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} unión(es) bridada(s) del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica {severidad}.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) de acero al carbono por elementos nuevos del mismo material, en las {cantidad} uniones bridadas afectadas, conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
+          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) de acero al carbono por elementos nuevos del mismo material, en {cantidad} unión(es) bridada(s) afectada(s), conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>cantidad_elementos=sus; severidad=severa</t>
+          <t>cantidad_elementos=sus; severidad=severa; cantidad=1</t>
         </is>
       </c>
     </row>
@@ -2041,6 +2041,80 @@
       <c r="G41" s="6" t="inlineStr">
         <is>
           <t>tipo=U-bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE_ABRAZADERA_AJENA_A_LINEA</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Abrazadera/soporte ajeno a la línea (pertenece a otro sistema)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Abrazadera tipo {tipo} instalada en la línea inspeccionada NPS {nps}, la cual sujeta un elemento de otro sistema (bandeja de cableado eléctrico o instrumentación) y no cumple ninguna función para esta línea.</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>El soporte o abrazadera no corresponde a la línea que se está inspeccionando; se debe solicitar el retiro y reubicación de dicho elemento, de acuerdo a los procedimientos Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>tipo=U-bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE_ABRAZADERA_MAL_POSICIONADA</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Abrazadera mal posicionada/instalada</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Abrazadera mal posicionada, ubicada en {ubicacion} de la tubería NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Se recomienda la corrección de la instalación de la abrazadera con respecto a la tubería NPS {nps}, de acuerdo a los procedimientos Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>ubicacion, nps</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>ubicacion=el tramo observado</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3259,6 +3333,202 @@
       </c>
       <c r="F49" s="6" t="inlineStr"/>
     </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE_ABRAZADERA_AJENA_A_LINEA</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>CUALQUIERA</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>abrazadera | soporte</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE_ABRAZADERA_AJENA_A_LINEA</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>CUALQUIERA</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>no cumple ninguna funcion | no cumple ninguna función | no comple ninguna funcion | no comple ninguna función | no corresponde a la linea | no corresponde a la línea | no corresponde a esta linea | no corresponde a esta línea | no pertenece a la linea | no pertenece a la línea | ajena a la linea | ajena a la línea | otro sistema</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE_ABRAZADERA_MAL_POSICIONADA</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>CUALQUIERA</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>abrazadera</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE_ABRAZADERA_MAL_POSICIONADA</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>CUALQUIERA</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>mal posicionada | mal posicionado | mal ubicada | mal ubicado | posicion incorrecta</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>BRIDA_PAR_GALVANICO_PARCIAL</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>par galvanico parcial | par galvánico parcial</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>BRIDA_PAR_GALVANICO_PARCIAL</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>moderada</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>BRIDA_PAR_GALVANICO_PARCIAL_SEVERA</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>par galvanico parcial | par galvánico parcial</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>BRIDA_PAR_GALVANICO_PARCIAL_SEVERA</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>El soporte o abrazadera no corresponde a la línea que se está inspeccionando; se debe solicitar el retiro y reubicación de dicho elemento, de acuerdo a los procedimientos Repsol aplicables.</t>
+          <t>Realizar el retiro y reubicación del soporte que está sujetado a la línea inspeccionada mediante la abrazadera tipo {tipo}, de acuerdo a los procedimientos Repsol aplicables.</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -736,29 +736,29 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión {severidad} generalizada en {elemento} (tramo/circuito NPS {nps}, longitud aprox. {longitud} metros).</t>
+          <t>Deterioro del recubrimiento y corrosión generalizada en {elemento} (circuito NPS {nps}, longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento en la totalidad del recubrimiento de {elemento} pertenecientes al tramo/circuito NPS {nps} (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento en la totalidad del recubrimiento (pintura) del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>severidad, elemento, nps, longitud</t>
+          <t>elemento, nps, longitud</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>severidad=leve a moderada; elemento=los accesorios y componentes</t>
+          <t>elemento=los accesorios y componentes</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>TUBERIA_JUNTAS_SOLDADAS_SIN_PINTURA</t>
+          <t>TUBERIA_DETERIORO_RECUBRIMIENTO_PARCIAL</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -768,89 +768,93 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Juntas soldadas nuevas sin pintura</t>
+          <t>Deterioro de recubrimiento parcial en tramo de línea</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Corrosión leve en la zona de {cantidad} juntas soldadas sin recubrimiento protector (pintura) perteneciente al tramo nuevo del circuito NPS {nps}.</t>
+          <t>Deterioro del recubrimiento y corrosión leve a moderada en {elemento} (tramo NPS {nps}, longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Realizar la aplicación del recubrimiento protector (pintura) en las {cantidad} juntas soldadas del tramo nuevo del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento del recubrimiento (pintura) en un tramo de NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>cantidad, nps</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
+          <t>elemento, nps, longitud</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>elemento=los accesorios y componentes</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>TUBERIA_JUNTAS_SOLDADAS_SIN_PINTURA</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Juntas soldadas nuevas sin pintura</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Corrosión leve en la zona de {cantidad} juntas soldadas sin recubrimiento protector (pintura) perteneciente al tramo nuevo del circuito NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Realizar la aplicación del recubrimiento protector (pintura) en las {cantidad} juntas soldadas del tramo nuevo del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>cantidad, nps</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>TUBERIA_PANDEO_DEFORMACION</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>TUBERIA</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Deformación o pandeo en tuberías</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Pandeo / Deformación en la tubería cerca de {ubicacion} (NPS {nps}, longitud aprox. {longitud} metros).</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Recomendación:
 • Realizar la evaluación de integridad mecánica en el tramo de tubería de NPS {nps} y una longitud de {longitud} metros, cerca de {ubicacion}, afectado por deformación y pandeo, conforme a los lineamientos del código API 570 y los estándares Repsol aplicables.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>ubicacion, nps, longitud</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>TUBERIA_TRAMO_NO_ACCESIBLE</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>TUBERIA</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Tramo del circuito en altura / no accesible</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Presencia de corrosión (otros) en tramo no accesible: circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Se requiere instalar facilidades (andamios de {longitud} metros) para acceder a la zona cerca de {ubicacion} y complementar la inspección de la zona observada en la tubería de NPS {nps}.</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>nps, longitud, ubicacion</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -858,7 +862,7 @@
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>TUBERIA_COLOR_NO_REGLAMENTARIO</t>
+          <t>TUBERIA_TRAMO_NO_ACCESIBLE</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -868,22 +872,22 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Adecuación por código de color no reglamentario</t>
+          <t>Tramo del circuito en altura / no accesible</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Recubrimiento existente en color no reglamentario ({color_actual}) en el circuito NPS {nps}, requiriendo el código de color de identificación ({color_norma}).</t>
+          <t>Presencia de corrosión (otros) en tramo no accesible: circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Realizar la aplicación de la capa de acabado/repintado del circuito NPS {nps}, para adecuarlo al color de identificación correspondiente al fluido transportado ({color_norma}), en conformidad con el estándar Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Se requiere instalar facilidades (andamios de {longitud} metros) para acceder a la zona cerca de {ubicacion} y complementar la inspección de la zona observada en la tubería de NPS {nps}.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>color_actual, nps, color_norma</t>
+          <t>nps, longitud, ubicacion</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
@@ -891,32 +895,32 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>VALVULA_MANUAL_CORROSION_MODERADA</t>
+          <t>TUBERIA_COLOR_NO_REGLAMENTARIO</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>VALVULA</t>
+          <t>TUBERIA</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Válvula manual con corrosión moderada</t>
+          <t>Adecuación por código de color no reglamentario</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión moderada en válvula de {tipo} NPS {nps}.</t>
+          <t>Recubrimiento existente en color no reglamentario ({color_actual}) en el circuito NPS {nps}, requiriendo el código de color de identificación ({color_norma}).</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento del recubrimiento en la válvula de {tipo} NPS {nps}, incluyendo el mantenimiento de los mecanismos del volante, bonete y prensaestopas, así como su lubricación, según los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar la aplicación de la capa de acabado/repintado del circuito NPS {nps}, para adecuarlo al color de identificación correspondiente al fluido transportado ({color_norma}), en conformidad con el estándar Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>tipo, nps</t>
+          <t>color_actual, nps, color_norma</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
@@ -924,7 +928,7 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>VALVULA_CORROSION_SEVERA_PERNOS</t>
+          <t>VALVULA_MANUAL_CORROSION_MODERADA</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -934,22 +938,22 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Válvula con corrosión moderada a severa en pernos y mecanismos</t>
+          <t>Válvula manual con corrosión moderada</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión moderada a severa en {cantidad} válvulas de {tipo} de NPS {nps}, afectando principalmente a los pernos de ajuste del volante y de la prensaestopas.</t>
+          <t>Deterioro del recubrimiento y corrosión moderada en válvula de {tipo} NPS {nps}.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en las {cantidad} válvulas de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3. (Nota: al ser corrosión severa, se excluye el mantenimiento rutinario de recubrimiento).</t>
+          <t>Efectuar el mantenimiento del recubrimiento en la válvula de {tipo} NPS {nps}, incluyendo el mantenimiento de los mecanismos del volante, bonete y prensaestopas, así como su lubricación, según los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>cantidad, tipo, nps</t>
+          <t>tipo, nps</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr"/>
@@ -957,139 +961,139 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>VALVULA_CORROSION_SEVERA_PERNOS</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Válvula con corrosión moderada a severa en pernos y mecanismos</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Deterioro del recubrimiento y corrosión moderada a severa en {cantidad} válvulas de {tipo} de NPS {nps}, afectando principalmente a los pernos de ajuste del volante y de la prensaestopas.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en las {cantidad} válvulas de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3. (Nota: al ser corrosión severa, se excluye el mantenimiento rutinario de recubrimiento).</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>cantidad, tipo, nps</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>VALVULA_VOLANTE_SUELTO</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>VALVULA</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Volante desprendido o suelto</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Volante fuera de posición (desprendido del vástago) y sujetado provisoriamente con alambre de amarre en válvula de {tipo} de NPS {nps}.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Realizar el mantenimiento correctivo o reemplazo de la válvula de {tipo} de NPS {nps}, reinstalando y fijando de manera definitiva el volante al vástago, conforme a la norma API 598 y estándares Repsol aplicables.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>tipo, nps</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>VALVULA_AGUJA_PERDIDA_MANIVELA</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>VALVULA</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Pérdida de manivela/palanca en válvula de aguja</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Pérdida de la manivela / palanca de accionamiento en la válvula de {tipo} de NPS {nps}, de bloqueo y purga del indicador de presión manómetro.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Realizar el reemplazo de la manivela de la válvula de aguja de NPS {nps} para restablecer la maniobrabilidad del elemento de bloqueo y purga, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>tipo, nps</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>VALVULA_AGUJA_PERDIDA_MANIVELA</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Pérdida de manivela/palanca en válvula de aguja</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Pérdida de la manivela / palanca de accionamiento en la válvula de {tipo} de NPS {nps}, de bloqueo y purga del indicador de presión manómetro.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo de la manivela de la válvula de aguja de NPS {nps} para restablecer la maniobrabilidad del elemento de bloqueo y purga, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>VALVULA_PERDIDA_VOLANTE</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>VALVULA</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Pérdida o rotura de volante en válvula de compuerta, globo</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Pérdida, rotura de la volante en la válvulas de {tipo} de NPS {nps}.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Realizar el reemplazo del volante en la válvula de {tipo} de NPS {nps}, conforme a la norma API 598 y estándares Repsol aplicables.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>tipo, nps</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>VALVULA_FUGA_PRENSAESTOPAS</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>VALVULA</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Residuos de producto / fuga en prensaestopas</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Presencia de restos de producto (humedecido) en la zona de la prensaestopas en {cantidad} válvulas de {tipo} de NPS {nps}.</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Realizar el mantenimiento correctivo de las {cantidad} válvulas de {tipo} de NPS {nps}, incluyendo la limpieza integral del producto adherido, inspección de sus componentes, de acuerdo con la práctica recomendada API 598 y los estándares Repsol aplicables.</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>cantidad, tipo, nps</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>VALVULA_LINEA_AISLADA_SIN_AISLAMIENTO_PROPIO</t>
+          <t>VALVULA_FUGA_PRENSAESTOPAS</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1099,22 +1103,22 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Válvula en línea aislada sin aislamiento propio</t>
+          <t>Residuos de producto / fuga en prensaestopas</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Presencia de corrosión generalizada en {cantidad} válvulas sin aislamiento térmico ({tipo}) en línea aislada.</t>
+          <t>Presencia de restos de producto (humedecido) en la zona de la prensaestopas en {cantidad} válvulas de {tipo} de NPS {nps}.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza en {cantidad} válvulas ({tipo}) y mantenimiento de elementos de ajuste (espárragos y tuercas), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006. NOTA: si la línea con aislamiento térmico excede los 200 °C, ya no corresponde aplicar recubrimiento (pintura).</t>
+          <t>Realizar el mantenimiento correctivo de las {cantidad} válvulas de {tipo} de NPS {nps}, incluyendo la limpieza integral del producto adherido, inspección de sus componentes, de acuerdo con la práctica recomendada API 598 y los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>cantidad, tipo</t>
+          <t>cantidad, tipo, nps</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
@@ -1122,7 +1126,7 @@
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>VALVULA_CONTROL_FUGA_CUERPO_BONETE</t>
+          <t>VALVULA_LINEA_AISLADA_SIN_AISLAMIENTO_PROPIO</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1132,22 +1136,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Válvula de control con fuga cuerpo-bonete</t>
+          <t>Válvula en línea aislada sin aislamiento propio</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Fuga de producto / restos de producto en la unión entre cuerpo y bonete en válvula de control de tipo {tipo} de NPS {nps} ({tag}).</t>
+          <t>Presencia de corrosión generalizada en {cantidad} válvulas sin aislamiento térmico ({tipo}) en línea aislada.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento correctivo de la unión cuerpo-bonete y reemplazo del empaque/junta en la válvula de control {tag} / NPS {nps}, así como la limpieza integral del producto acumulado, siguiendo los lineamientos del código API 570 y los estándares Repsol aplicables.</t>
+          <t>Realizar limpieza en {cantidad} válvulas ({tipo}) y mantenimiento de elementos de ajuste (espárragos y tuercas), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006. NOTA: si la línea con aislamiento térmico excede los 200 °C, ya no corresponde aplicar recubrimiento (pintura).</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>tipo, nps, tag</t>
+          <t>cantidad, tipo</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr"/>
@@ -1155,7 +1159,7 @@
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>VALVULA_CONTROL_SUCIEDAD_EXTERNA</t>
+          <t>VALVULA_CONTROL_FUGA_CUERPO_BONETE</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1165,22 +1169,22 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Válvula de control con suciedad externa en instrumentación</t>
+          <t>Válvula de control con fuga cuerpo-bonete</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Presencia de suciedad en componentes externos (bonete, eje, indicador y métrica de posición) de la válvula de control {tag} / NPS {nps}.</t>
+          <t>Fuga de producto / restos de producto en la unión entre cuerpo y bonete en válvula de control de tipo {tipo} de NPS {nps} ({tag}).</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza de los componentes afectados de la válvula de control {tag} / NPS {nps}, conforme a los estándares de mantenimiento de instrumentación y lineamientos Repsol aplicables.</t>
+          <t>Realizar el mantenimiento correctivo de la unión cuerpo-bonete y reemplazo del empaque/junta en la válvula de control {tag} / NPS {nps}, así como la limpieza integral del producto acumulado, siguiendo los lineamientos del código API 570 y los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>tag, nps</t>
+          <t>tipo, nps, tag</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr"/>
@@ -1188,32 +1192,32 @@
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_UBOLT_CONTACTO_DIRECTO</t>
+          <t>VALVULA_CONTROL_SUCIEDAD_EXTERNA</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE</t>
+          <t>VALVULA</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Soporte U-bolt con corrosión moderada y contacto directo</t>
+          <t>Válvula de control con suciedad externa en instrumentación</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Soporte con abrazadera tipo U-bolt presenta corrosión moderada y contacto directo con tubería NPS {nps}.</t>
+          <t>Presencia de suciedad en componentes externos (bonete, eje, indicador y métrica de posición) de la válvula de control {tag} / NPS {nps}.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento del recubrimiento en soporte y abrazadera tipo U-bolt e instalar un aislamiento de protección (teflón, elastómero o neopreno) para evitar el contacto directo metal-metal en la tubería NPS {nps}, de acuerdo con la norma MSS SP-58 y los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5).</t>
+          <t>Realizar limpieza de los componentes afectados de la válvula de control {tag} / NPS {nps}, conforme a los estándares de mantenimiento de instrumentación y lineamientos Repsol aplicables.</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>nps</t>
+          <t>tag, nps</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr"/>
@@ -1221,67 +1225,67 @@
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>SOPORTE_UBOLT_CONTACTO_DIRECTO</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Soporte U-bolt con corrosión moderada y contacto directo</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Soporte con abrazadera tipo U-bolt presenta corrosión moderada y contacto directo con tubería NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento del recubrimiento en soporte y abrazadera tipo U-bolt e instalar un aislamiento de protección (teflón, elastómero o neopreno) para evitar el contacto directo metal-metal en la tubería NPS {nps}, de acuerdo con la norma MSS SP-58 y los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5).</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t>SOPORTE_LEVE_ABRAZADERA_SEVERA</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>SOPORTE</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Soporte con corrosión leve y abrazadera/pernos con corrosión severa</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Deterioro del recubrimiento y corrosión leve por sectores en soporte, y corrosión severa en la abrazadera y sus pernos de ajuste (línea NPS {nps}).</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Recomendación:
 • Realizar el reemplazo de la abrazadera y sus pernos de ajuste en la línea NPS {nps}, de acuerdo con la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a (sección 5.5).
 • Nota: si el soporte solo cuenta con corrosión leve y no afecta su integridad, no se recomienda acción correctiva o preventiva sobre el soporte.</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>nps</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>SOPORTE_REEMPLAZO_TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>SOPORTE</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Reemplazo total de soporte y abrazadera (corrosión severa)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Deterioro del recubrimiento, corrosión moderada y severa en soporte y abrazaderas ({cantidad}) en el tramo de la línea NPS {nps}.</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Realizar el reemplazo del soporte y de las {cantidad} abrazaderas en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58. (Sin mantenimiento de recubrimiento/pintura).</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>cantidad, nps</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr"/>
@@ -1289,7 +1293,7 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_METALICO_TIPICO</t>
+          <t>SOPORTE_REEMPLAZO_TOTAL</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1299,34 +1303,30 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Deterioro de recubrimiento y corrosión leve a moderada en soporte metálico típico</t>
+          <t>Reemplazo total de soporte y abrazadera (corrosión severa)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión {severidad} en el soporte tipo {tipo} de la línea NPS {nps}.</t>
+          <t>Deterioro del recubrimiento, corrosión moderada y severa en soporte y abrazaderas ({cantidad}) en el tramo de la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo {tipo} de la línea NPS {nps}. La intervención deberá realizarse conforme al esquema de pinturas PE-B-0600.01-I, aplicando como color de acabado el verde RAL 6001.</t>
+          <t>Realizar el reemplazo del soporte y de las {cantidad} abrazaderas en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58. (Sin mantenimiento de recubrimiento/pintura).</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>severidad, tipo, nps</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>severidad=leve a moderada</t>
-        </is>
-      </c>
+          <t>cantidad, nps</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_SPRING_HANGER</t>
+          <t>SOPORTE_METALICO_TIPICO</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1336,50 +1336,54 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Soporte tipo resorte (spring hanger) con corrosión moderada</t>
+          <t>Deterioro de recubrimiento y corrosión leve a moderada en soporte metálico típico</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión moderada en soporte de resorte (spring hanger) de la línea NPS {nps}.</t>
+          <t>Deterioro del recubrimiento y corrosión {severidad} en el soporte tipo {tipo} de la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo spring hanger de la línea NPS {nps}, conforme a los estándares Repsol ED-B-06.00-04d y al documento técnico PE-B-0600.01H00R05. (No se especifica código de color de acabado por sus consideraciones especiales frente a otros soportes).</t>
+          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo {tipo} de la línea NPS {nps}. La intervención deberá realizarse conforme al esquema de pinturas PE-B-0600.01-I, aplicando como color de acabado el verde RAL 6001.</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>nps</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
+          <t>severidad, tipo, nps</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>severidad=leve a moderada</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>AISLAMIENTO_VENTANA_INSPECCION</t>
+          <t>SOPORTE_SPRING_HANGER</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>AISLAMIENTO</t>
+          <t>SOPORTE</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Contaminación/corrosión moderada en ventana de inspección</t>
+          <t>Soporte tipo resorte (spring hanger) con corrosión moderada</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Contaminación del aislamiento térmico (humedad), así como también se visualiza corrosión moderada en zonas con ventanas de inspección (línea NPS {nps}).</t>
+          <t>Deterioro del recubrimiento y corrosión moderada en soporte de resorte (spring hanger) de la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Retirar el aislamiento térmico y efectuar la limpieza de la zona corroída para evaluar el grado de daño. En caso de verificarse corrosión superficial, aplicar recubrimiento de pintura, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05. Nota: solo se aplica recubrimiento a tuberías con temperatura de operación menor o igual a 200 °C.</t>
+          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo spring hanger de la línea NPS {nps}, conforme a los estándares Repsol ED-B-06.00-04d y al documento técnico PE-B-0600.01H00R05. (No se especifica código de color de acabado por sus consideraciones especiales frente a otros soportes).</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1392,7 +1396,7 @@
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>AISLAMIENTO_ABERTURAS_ABOLLADURAS</t>
+          <t>AISLAMIENTO_VENTANA_INSPECCION</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1402,22 +1406,22 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Aberturas, abolladuras o exposición del aislante</t>
+          <t>Contaminación/corrosión moderada en ventana de inspección</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Abertura(s) en la cubierta metálica, abolladuras, deterioro y/o exposición del material aislante en {ubicacion} del circuito NPS {nps}.</t>
+          <t>Contaminación del aislamiento térmico (humedad), así como también se visualiza corrosión moderada en zonas con ventanas de inspección (línea NPS {nps}).</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Reparar el aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Retirar el aislamiento térmico y efectuar la limpieza de la zona corroída para evaluar el grado de daño. En caso de verificarse corrosión superficial, aplicar recubrimiento de pintura, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05. Nota: solo se aplica recubrimiento a tuberías con temperatura de operación menor o igual a 200 °C.</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>ubicacion, nps</t>
+          <t>nps</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr"/>
@@ -1425,7 +1429,7 @@
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>AISLAMIENTO_AUSENCIA</t>
+          <t>AISLAMIENTO_ABERTURAS_ABOLLADURAS</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1435,22 +1439,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Ausencia / falta de aislamiento térmico</t>
+          <t>Aberturas, abolladuras o exposición del aislante</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de aislamiento térmico en {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros).</t>
+          <t>Abertura(s) en la cubierta metálica, abolladuras, deterioro y/o exposición del material aislante en {ubicacion} del circuito NPS {nps}.</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Instalar aislamiento térmico en {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros), siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Reparar el aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>ubicacion, nps, longitud</t>
+          <t>ubicacion, nps</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -1458,7 +1462,7 @@
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>AISLAMIENTO_MANCHAS_SUCIEDAD</t>
+          <t>AISLAMIENTO_AUSENCIA</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1468,22 +1472,22 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Manchas de producto, suciedad o deterioro superficial del aislamiento</t>
+          <t>Ausencia / falta de aislamiento térmico</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Presencia de manchas de producto, suciedad o deterioro en el aislamiento térmico en {cantidad} zonas del circuito (longitud aprox. {longitud} metros).</t>
+          <t>Ausencia de aislamiento térmico en {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Instalar aislamiento térmico en {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros), siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>cantidad, longitud, ubicacion</t>
+          <t>ubicacion, nps, longitud</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -1491,7 +1495,7 @@
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>AISLAMIENTO_PROTECCION_IGNIFUGA_AGRIETADA</t>
+          <t>AISLAMIENTO_MANCHAS_SUCIEDAD</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1501,22 +1505,22 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Protección ignífuga agrietada (fireproofing)</t>
+          <t>Manchas de producto, suciedad o deterioro superficial del aislamiento</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Agrietamiento en la protección ignífuga de {elemento} en la zona cercana a {ubicacion}.</t>
+          <t>Presencia de manchas de producto, suciedad o deterioro en el aislamiento térmico en {cantidad} zonas del circuito (longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Realizar la reparación de la protección ignífuga en {elemento}, asegurando el resane de las grietas, conforme a los lineamientos de los estándares Repsol aplicables.</t>
+          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>elemento, ubicacion</t>
+          <t>cantidad, longitud, ubicacion</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -1524,32 +1528,32 @@
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>INDICADOR_MANOMETRO_DETERIORADO</t>
+          <t>AISLAMIENTO_PROTECCION_IGNIFUGA_AGRIETADA</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INDICADOR</t>
+          <t>AISLAMIENTO</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Manómetro con deterioro, aguja desprendida y opacidad en visor</t>
+          <t>Protección ignífuga agrietada (fireproofing)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Manómetro con deterioro, aguja desprendida, contaminación de glicerina e imposibilidad de toma de lectura por opacidad del visor en línea NPS {nps}.</t>
+          <t>Agrietamiento en la protección ignífuga de {elemento} en la zona cercana a {ubicacion}.</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo del manómetro en la línea NPS {nps} para garantizar la confiabilidad en la lectura del instrumento y mantener la integridad operacional, conforme a los estándares de instrumentación y lineamientos Repsol aplicables.</t>
+          <t>Realizar la reparación de la protección ignífuga en {elemento}, asegurando el resane de las grietas, conforme a los lineamientos de los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>nps</t>
+          <t>elemento, ubicacion</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
@@ -1557,27 +1561,27 @@
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_ESPARRAGOS_CORTOS</t>
+          <t>INDICADOR_MANOMETRO_DETERIORADO</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>BRIDA</t>
+          <t>INDICADOR</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Espárragos cortos (longitud insuficiente)</t>
+          <t>Manómetro con deterioro, aguja desprendida y opacidad en visor</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Longitud insuficiente de espárragos en unión bridada de NPS {nps} (no sobresalen de la cara exterior de la tuerca).</t>
+          <t>Manómetro con deterioro, aguja desprendida, contaminación de glicerina e imposibilidad de toma de lectura por opacidad del visor en línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Reemplazar los espárragos por unos de longitud adecuada que garanticen sobresalir al menos dos (2) hilos de rosca por encima de la cara exterior de la tuerca, conforme a la norma ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Realizar el reemplazo del manómetro en la línea NPS {nps} para garantizar la confiabilidad en la lectura del instrumento y mantener la integridad operacional, conforme a los estándares de instrumentación y lineamientos Repsol aplicables.</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1590,151 +1594,147 @@
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>BRIDA_ESPARRAGOS_CORTOS</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Espárragos cortos (longitud insuficiente)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Hallazgo: Longitud insuficiente de espárragos en unión bridada de NPS {nps} (no sobresalen de la cara exterior de la tuerca).</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Reemplazar los espárragos por unos de longitud adecuada que garanticen sobresalir al menos dos (2) hilos de rosca por encima de la cara exterior de la tuerca, conforme a la norma ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>BRIDA_PAR_GALVANICO</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>BRIDA</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Par galvánico (bridas inox + espárragos acero al carbono)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Hallazgo: Par galvánico por incompatibilidad de materiales (bridas de acero inoxidable con espárragos y tuercas de acero al carbono) en {cantidad} uniones bridadas del circuito NPS {nps}.</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Realizar el reemplazo de la totalidad de los elementos de ajuste de acero al carbono por espárragos y tuercas de acero inoxidable de grado compatible, conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>cantidad, nps</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BRIDA_PAR_GALVANICO_PARCIAL</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>BRIDA</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Par galvánico parcial (1 brida inox + 1 brida acero al carbono), corrosión moderada</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} unión(es) bridada(s) del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica moderada.</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Realizar el mantenimiento de los elementos de ajuste de acero al carbono (espárragos y tuercas) en {cantidad} unión(es) bridada(s) afectada(s), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>cantidad, cantidad_elementos, nps</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>cantidad_elementos=sus; cantidad=1</t>
-        </is>
-      </c>
+      <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>BRIDA_PAR_GALVANICO_PARCIAL</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Par galvánico parcial (1 brida inox + 1 brida acero al carbono), corrosión moderada</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} unión(es) bridada(s) del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica moderada.</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento de los elementos de ajuste de acero al carbono (espárragos y tuercas) en {cantidad} unión(es) bridada(s) afectada(s), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>cantidad, cantidad_elementos, nps</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>cantidad_elementos=sus; cantidad=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>BRIDA_PAR_GALVANICO_PARCIAL_SEVERA</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>BRIDA</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Par galvánico parcial (1 brida inox + 1 brida acero al carbono), corrosión severa</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Par galvánico por incompatibilidad de materiales (1 brida de acero inoxidable y 1 brida de acero al carbono) en {cantidad} unión(es) bridada(s) del circuito NPS {nps}, cada una con {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono, los cuales presentan corrosión galvánica {severidad}.</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) de acero al carbono por elementos nuevos del mismo material, en {cantidad} unión(es) bridada(s) afectada(s), conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>cantidad, cantidad_elementos, nps, severidad</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>cantidad_elementos=sus; severidad=severa; cantidad=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>BRIDA_CORROSION_LEVE_MODERADA</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>BRIDA</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Corrosión en espárragos/bridas (leve a moderada)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Hallazgo: Deterioro del recubrimiento y presencia de corrosión {severidad} en {cantidad} uniones bridadas, incluyendo sus elementos de ajuste (espárragos y tuercas) en la línea NPS {nps}.</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} uniones bridadas, incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>severidad, cantidad, nps</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>severidad=leve a moderada</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_SEVERA_ESPARRAGOS_MODERADA_BRIDA</t>
+          <t>BRIDA_CORROSION_LEVE_MODERADA</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1744,30 +1744,34 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Corrosión severa en espárragos y moderada en bridas</t>
+          <t>Corrosión en espárragos/bridas (leve a moderada)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Deterioro del recubrimiento y corrosión moderada en bridas, con corrosión severa en espárragos y tuercas en {cantidad} uniones bridadas de NPS {nps}.</t>
+          <t>Hallazgo: Deterioro del recubrimiento y presencia de corrosión {severidad} en {cantidad} uniones bridadas, incluyendo sus elementos de ajuste (espárragos y tuercas) en la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) en las {cantidad} uniones bridadas de NPS {nps}, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 y ASME B31.3; asimismo, efectuar el mantenimiento del recubrimiento en las bridas según los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} uniones bridadas, incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>cantidad, nps</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
+          <t>severidad, cantidad, nps</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>severidad=leve a moderada</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_PERNOS_EN_LUGAR_DE_ESPARRAGOS</t>
+          <t>BRIDA_SEVERA_ESPARRAGOS_MODERADA_BRIDA</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1777,22 +1781,22 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Uso de pernos en lugar de espárragos</t>
+          <t>Corrosión severa en espárragos y moderada en bridas</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Unión bridada de NPS {nps} con uso de pernos en lugar de espárragos de ajuste ({cantidad} unidades).</t>
+          <t>Hallazgo: Deterioro del recubrimiento y corrosión moderada en bridas, con corrosión severa en espárragos y tuercas en {cantidad} uniones bridadas de NPS {nps}.</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Reemplazar los pernos por espárragos con tuercas en la unión bridada NPS {nps}, garantizando que sobresalgan al menos dos (2) hilos de rosca, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) en las {cantidad} uniones bridadas de NPS {nps}, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 y ASME B31.3; asimismo, efectuar el mantenimiento del recubrimiento en las bridas según los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>nps, cantidad</t>
+          <t>cantidad, nps</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
@@ -1800,7 +1804,7 @@
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_TUERCA_FALTANTE</t>
+          <t>BRIDA_PERNOS_EN_LUGAR_DE_ESPARRAGOS</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1810,22 +1814,22 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Falta de elemento de ajuste (tuerca faltante)</t>
+          <t>Uso de pernos en lugar de espárragos</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Ausencia de tuerca hexagonal en {cantidad} espárrago(s) de la junta bridada de NPS {nps}.</t>
+          <t>Hallazgo: Unión bridada de NPS {nps} con uso de pernos en lugar de espárragos de ajuste ({cantidad} unidades).</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Instalar la tuerca hexagonal faltante en el espárrago de la junta bridada de NPS {nps} y aplicar apriete/torque verificado para garantizar un sellado uniforme, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Reemplazar los pernos por espárragos con tuercas en la unión bridada NPS {nps}, garantizando que sobresalgan al menos dos (2) hilos de rosca, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>cantidad, nps</t>
+          <t>nps, cantidad</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
@@ -1833,7 +1837,7 @@
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_FUGA_EMPAQUE</t>
+          <t>BRIDA_TUERCA_FALTANTE</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1843,22 +1847,22 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Fuga de producto / falla de empaque</t>
+          <t>Falta de elemento de ajuste (tuerca faltante)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Presencia de fuga de producto / restos humedecidos en la junta bridada de NPS {nps}.</t>
+          <t>Hallazgo: Ausencia de tuerca hexagonal en {cantidad} espárrago(s) de la junta bridada de NPS {nps}.</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento de la unión bridada NPS {nps} mediante limpieza de caras, cambio de empaque y torqueado controlado conforme al código API 570, ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Instalar la tuerca hexagonal faltante en el espárrago de la junta bridada de NPS {nps} y aplicar apriete/torque verificado para garantizar un sellado uniforme, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>nps</t>
+          <t>cantidad, nps</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -1866,32 +1870,32 @@
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_ORIFICIO_FALTA_SOLDADURA_SELLO</t>
+          <t>BRIDA_FUGA_EMPAQUE</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_ORIFICIO</t>
+          <t>BRIDA</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Falta de soldadura de sello en niples de toma de brida de orificio</t>
+          <t>Fuga de producto / falla de empaque</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Se identificó ausencia de soldadura de sello entre los 2 niples NPS ½” (tomas alta y baja presión) y las bridas de la placa orificio ({tag}).</t>
+          <t>Hallazgo: Presencia de fuga de producto / restos humedecidos en la junta bridada de NPS {nps}.</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
+          <t>Realizar el mantenimiento de la unión bridada NPS {nps} mediante limpieza de caras, cambio de empaque y torqueado controlado conforme al código API 570, ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>nps</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
@@ -1899,81 +1903,77 @@
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>VALVULA_VOLANTE_AUSENTE</t>
+          <t>BRIDA_ORIFICIO_FALTA_SOLDADURA_SELLO</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>VALVULA</t>
+          <t>BRIDA_ORIFICIO</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Ausencia total de volante en válvula</t>
+          <t>Falta de soldadura de sello en niples de toma de brida de orificio</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de volante en {cantidad} válvula(s) de {tipo} de NPS {nps}.</t>
+          <t>Se identificó ausencia de soldadura de sello entre los 2 niples NPS ½” (tomas alta y baja presión) y las bridas de la placa orificio ({tag}).</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Realizar la instalación de un volante nuevo en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a la norma API 598 y estándares Repsol aplicables.</t>
+          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>cantidad, tipo, nps</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>cantidad=1; tipo=compuerta</t>
-        </is>
-      </c>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr"/>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_FALTANTE</t>
+          <t>VALVULA_VOLANTE_AUSENTE</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE</t>
+          <t>VALVULA</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Ausencia total de soporte</t>
+          <t>Ausencia total de volante en válvula</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de soporte en {ubicacion} de la línea NPS {nps}.</t>
+          <t>Ausencia de volante en {cantidad} válvula(s) de {tipo} de NPS {nps}.</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Realizar la instalación de un soporte en {ubicacion} de la línea NPS {nps}, conforme a los procedimientos específicos y estándares Repsol aplicables (ED-L-06.00-05a, sección 5.5, y la norma MSS SP-58).</t>
+          <t>Realizar la instalación de un volante nuevo en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a la norma API 598 y estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>ubicacion, nps</t>
+          <t>cantidad, tipo, nps</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>ubicacion=el tramo observado</t>
+          <t>cantidad=1; tipo=compuerta</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_ABRAZADERA_ROTA</t>
+          <t>SOPORTE_FALTANTE</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -1983,34 +1983,34 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Rotura de abrazadera</t>
+          <t>Ausencia total de soporte</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Rotura de la abrazadera tipo {tipo} en la línea NPS {nps}.</t>
+          <t>Ausencia de soporte en {ubicacion} de la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de la abrazadera tipo {tipo} en la línea NPS {nps}, conforme a la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a (sección 5.5).</t>
+          <t>Realizar la instalación de un soporte en {ubicacion} de la línea NPS {nps}, conforme a los procedimientos específicos y estándares Repsol aplicables (ED-L-06.00-05a, sección 5.5, y la norma MSS SP-58).</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>tipo, nps</t>
+          <t>ubicacion, nps</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>tipo=U-bolt</t>
+          <t>ubicacion=el tramo observado</t>
         </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_ABRAZADERA_FALTANTE</t>
+          <t>SOPORTE_ABRAZADERA_ROTA</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2020,17 +2020,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Ausencia total de abrazadera</t>
+          <t>Rotura de abrazadera</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de abrazadera tipo {tipo} en la línea NPS {nps}.</t>
+          <t>Rotura de la abrazadera tipo {tipo} en la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Realizar la instalación de una abrazadera tipo {tipo} en la línea NPS {nps}, conforme a la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a.</t>
+          <t>Realizar el reemplazo de la abrazadera tipo {tipo} en la línea NPS {nps}, conforme a la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a (sección 5.5).</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="42" ht="45" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE_ABRAZADERA_AJENA_A_LINEA</t>
+          <t>SOPORTE_ABRAZADERA_FALTANTE</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2057,17 +2057,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Abrazadera/soporte ajeno a la línea (pertenece a otro sistema)</t>
+          <t>Ausencia total de abrazadera</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Abrazadera tipo {tipo} instalada en la línea inspeccionada NPS {nps}, la cual sujeta un elemento de otro sistema (bandeja de cableado eléctrico o instrumentación) y no cumple ninguna función para esta línea.</t>
+          <t>Ausencia de abrazadera tipo {tipo} en la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Realizar el retiro y reubicación del soporte que está sujetado a la línea inspeccionada mediante la abrazadera tipo {tipo}, de acuerdo a los procedimientos Repsol aplicables.</t>
+          <t>Realizar la instalación de una abrazadera tipo {tipo} en la línea NPS {nps}, conforme a la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a.</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2084,35 +2084,72 @@
     <row r="43" ht="45" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
+          <t>SOPORTE_ABRAZADERA_AJENA_A_LINEA</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Abrazadera/soporte ajeno a la línea (pertenece a otro sistema)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Abrazadera tipo {tipo} instalada en la línea inspeccionada NPS {nps}, la cual sujeta un elemento de otro sistema (bandeja de cableado eléctrico o instrumentación) y no cumple ninguna función para esta línea.</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Realizar el retiro y reubicación del soporte que está sujetado a la línea inspeccionada mediante la abrazadera tipo {tipo}, de acuerdo a los procedimientos Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>tipo=U-bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
           <t>SOPORTE_ABRAZADERA_MAL_POSICIONADA</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>SOPORTE</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Abrazadera mal posicionada/instalada</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Abrazadera mal posicionada, ubicada en {ubicacion} de la tubería NPS {nps}.</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Se recomienda la corrección de la instalación de la abrazadera con respecto a la tubería NPS {nps}, de acuerdo a los procedimientos Repsol aplicables.</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>ubicacion, nps</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>ubicacion=el tramo observado</t>
         </is>
@@ -2130,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2216,7 +2253,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>generaliz | leve a moderada | leve  a moderada</t>
+          <t>generaliz</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr"/>
@@ -3507,27 +3544,55 @@
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>BRIDA_PAR_GALVANICO_PARCIAL_SEVERA</t>
+          <t>TUBERIA_DETERIORO_RECUBRIMIENTO_PARCIAL</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>generaliz</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>TUBERIA_DETERIORO_RECUBRIMIENTO_PARCIAL</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>severa</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>leve a moderada | leve  a moderada</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -773,12 +773,12 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión leve a moderada en {elemento} (tramo NPS {nps}, longitud aprox. {longitud} metros).</t>
+          <t>Deterioro del recubrimiento y corrosión leve a moderada en {elemento} (circuito NPS {nps}, longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento del recubrimiento (pintura) en un tramo de NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento en gran parte del recubrimiento (pintura) del circuito NPS {nps} (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -778,17 +778,17 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento en gran parte del recubrimiento (pintura) del circuito NPS {nps} (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento en gran parte del recubrimiento (pintura) del circuito NPS {nps}, en {cantidad} tramo(s) (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>elemento, nps, longitud</t>
+          <t>elemento, nps, longitud, cantidad</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>elemento=los accesorios y componentes</t>
+          <t>elemento=los accesorios y componentes; cantidad=1</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -778,17 +778,17 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento en gran parte del recubrimiento (pintura) del circuito NPS {nps}, en {cantidad} tramo(s) (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento del recubrimiento (pintura) del circuito NPS {nps} (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>elemento, nps, longitud, cantidad</t>
+          <t>elemento, nps, longitud</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>elemento=los accesorios y componentes; cantidad=1</t>
+          <t>elemento=los accesorios y componentes</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3543,30 +3543,25 @@
       <c r="F56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>TUBERIA_DETERIORO_RECUBRIMIENTO_PARCIAL</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>generaliz</t>
+      <c r="A57" t="n">
+        <v>26</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BRIDA_PAR_GALVANICO_PARCIAL_SEVERA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>severa</t>
         </is>
       </c>
     </row>
@@ -3585,14 +3580,42 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>generaliz</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>TUBERIA_DETERIORO_RECUBRIMIENTO_PARCIAL</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>leve a moderada | leve  a moderada</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>galvan | gálvan</t>
+          <t>galvan | gálvan | severa</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,11 @@
           <t>leve | moderada</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -3104,7 +3108,11 @@
           <t>leve | moderada</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>severa | spring hanger | u-bolt | u bolt | ubolt</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -3616,6 +3624,936 @@
         </is>
       </c>
       <c r="F59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>28</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TUBERIA_REEMPLAZO_TRAMO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>perdida de espesor | pérdida de espesor | perdida de espesores | pérdida de espesores</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>28</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TUBERIA_REEMPLAZO_TRAMO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>medicion de espesores | medición de espesores | verificado con medicion | verificado con medición</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>29</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TUBERIA_JUNTAS_SOLDADAS_SIN_PINTURA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>junta soldada | juntas soldadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>29</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TUBERIA_JUNTAS_SOLDADAS_SIN_PINTURA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>sin pintura | sin recubrimiento | tramo nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>VALVULA_CORROSION_SEVERA_PERNOS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>perno</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>30</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>VALVULA_CORROSION_SEVERA_PERNOS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>prensaestopas</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>30</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>VALVULA_CORROSION_SEVERA_PERNOS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>moderada a severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>31</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VALVULA_AGUJA_PERDIDA_MANIVELA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>manivela | palanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>31</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>VALVULA_AGUJA_PERDIDA_MANIVELA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>perdida | pérdida | ausencia | ausente | falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>32</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>VALVULA_FUGA_PRENSAESTOPAS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>prensaestopas</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>32</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>VALVULA_FUGA_PRENSAESTOPAS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>restos de producto | humedecido | fuga</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>33</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>VALVULA_LINEA_AISLADA_SIN_AISLAMIENTO_PROPIO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>sin aislamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>33</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VALVULA_LINEA_AISLADA_SIN_AISLAMIENTO_PROPIO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>linea aislada | línea aislada</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>34</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>VALVULA_CONTROL_FUGA_CUERPO_BONETE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>bonete</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>34</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VALVULA_CONTROL_FUGA_CUERPO_BONETE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>cuerpo</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>34</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VALVULA_CONTROL_FUGA_CUERPO_BONETE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>fuga | restos de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>35</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>VALVULA_CONTROL_SUCIEDAD_EXTERNA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>suciedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>35</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>VALVULA_CONTROL_SUCIEDAD_EXTERNA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>valvula de control | válvula de control</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>36</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SOPORTE_LEVE_ABRAZADERA_SEVERA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>36</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SOPORTE_LEVE_ABRAZADERA_SEVERA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>36</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SOPORTE_LEVE_ABRAZADERA_SEVERA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>abrazadera</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>36</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SOPORTE_LEVE_ABRAZADERA_SEVERA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>37</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SOPORTE_REEMPLAZO_TOTAL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>moderada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>37</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SOPORTE_REEMPLAZO_TOTAL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>37</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SOPORTE_REEMPLAZO_TOTAL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>37</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SOPORTE_REEMPLAZO_TOTAL</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>abrazadera</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>38</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>spring hanger</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>38</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>moderada</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>39</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_VENTANA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ventana de inspeccion | ventana de inspección | ventanas de inspeccion | ventanas de inspección</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>39</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_VENTANA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>corrosion | corrosión | contaminacion | contaminación</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>40</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_MANCHAS_SUCIEDAD</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>mancha</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>40</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_MANCHAS_SUCIEDAD</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>aislamiento termico | aislamiento térmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>41</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BRIDA_ESPARRAGOS_CORTOS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>esparrago | espárrago | esparragos | espárragos</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>41</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BRIDA_ESPARRAGOS_CORTOS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>longitud insuficiente | insuficiente longitud | no sobresalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>42</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BRIDA_PAR_GALVANICO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>par galvanico | par galvánico</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1 brida | una brida</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>43</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BRIDA_SEVERA_ESPARRAGOS_MODERADA_BRIDA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>esparrago | espárrago | esparragos | espárragos</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>43</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BRIDA_SEVERA_ESPARRAGOS_MODERADA_BRIDA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>43</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BRIDA_SEVERA_ESPARRAGOS_MODERADA_BRIDA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>moderada</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>44</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BRIDA_ORIFICIO_FALTA_SOLDADURA_SELLO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CUALQUIERA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>soldadura de sello</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>44</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BRIDA_ORIFICIO_FALTA_SOLDADURA_SELLO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CUALQUIERA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>niple | niples</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>bridas</t>
+          <t>bridas; placas orificio</t>
         </is>
       </c>
       <c r="D97" t="n">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -810,12 +810,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Corrosión leve en la zona de {cantidad} juntas soldadas sin recubrimiento protector (pintura) perteneciente al tramo nuevo del circuito NPS {nps}.</t>
+          <t>Corrosión leve en la zona de {cantidad} junta(s) soldada(s) sin recubrimiento protector (pintura) perteneciente al tramo nuevo del circuito NPS {nps}.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Realizar la aplicación del recubrimiento protector (pintura) en las {cantidad} juntas soldadas del tramo nuevo del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Realizar la aplicación del recubrimiento protector (pintura) en {cantidad} junta(s) soldada(s) del tramo nuevo del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -823,7 +823,11 @@
           <t>cantidad, nps</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -976,12 +980,12 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento y corrosión moderada a severa en {cantidad} válvulas de {tipo} de NPS {nps}, afectando principalmente a los pernos de ajuste del volante y de la prensaestopas.</t>
+          <t>Deterioro del recubrimiento y corrosión moderada a severa en {cantidad} válvula(s) de {tipo} de NPS {nps}, afectando principalmente a los pernos de ajuste del volante y de la prensaestopas.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en las {cantidad} válvulas de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3. (Nota: al ser corrosión severa, se excluye el mantenimiento rutinario de recubrimiento).</t>
+          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3. (Nota: al ser corrosión severa, se excluye el mantenimiento rutinario de recubrimiento).</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -989,7 +993,11 @@
           <t>cantidad, tipo, nps</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -1108,12 +1116,12 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Presencia de restos de producto (humedecido) en la zona de la prensaestopas en {cantidad} válvulas de {tipo} de NPS {nps}.</t>
+          <t>Presencia de restos de producto (humedecido) en la zona de la prensaestopas en {cantidad} válvula(s) de {tipo} de NPS {nps}.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento correctivo de las {cantidad} válvulas de {tipo} de NPS {nps}, incluyendo la limpieza integral del producto adherido, inspección de sus componentes, de acuerdo con la práctica recomendada API 598 y los estándares Repsol aplicables.</t>
+          <t>Realizar el mantenimiento correctivo de {cantidad} válvula(s) de {tipo} de NPS {nps}, incluyendo la limpieza integral del producto adherido, inspección de sus componentes, de acuerdo con la práctica recomendada API 598 y los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1121,7 +1129,11 @@
           <t>cantidad, tipo, nps</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -1141,12 +1153,12 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Presencia de corrosión generalizada en {cantidad} válvulas sin aislamiento térmico ({tipo}) en línea aislada.</t>
+          <t>Presencia de corrosión generalizada en {cantidad} válvula(s) sin aislamiento térmico ({tipo}) en línea aislada.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza en {cantidad} válvulas ({tipo}) y mantenimiento de elementos de ajuste (espárragos y tuercas), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006. NOTA: si la línea con aislamiento térmico excede los 200 °C, ya no corresponde aplicar recubrimiento (pintura).</t>
+          <t>Realizar limpieza en {cantidad} válvula(s) ({tipo}) y mantenimiento de elementos de ajuste (espárragos y tuercas), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006. NOTA: si la línea con aislamiento térmico excede los 200 °C, ya no corresponde aplicar recubrimiento (pintura).</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1154,7 +1166,11 @@
           <t>cantidad, tipo</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -1308,12 +1324,12 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Deterioro del recubrimiento, corrosión moderada y severa en soporte y abrazaderas ({cantidad}) en el tramo de la línea NPS {nps}.</t>
+          <t>Deterioro del recubrimiento, corrosión moderada y severa en soporte y {cantidad} abrazadera(s) en el tramo de la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo del soporte y de las {cantidad} abrazaderas en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58. (Sin mantenimiento de recubrimiento/pintura).</t>
+          <t>Realizar el reemplazo del soporte y de {cantidad} abrazadera(s) en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58. (Sin mantenimiento de recubrimiento/pintura).</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1321,7 +1337,11 @@
           <t>cantidad, nps</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -1510,7 +1530,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Presencia de manchas de producto, suciedad o deterioro en el aislamiento térmico en {cantidad} zonas del circuito (longitud aprox. {longitud} metros).</t>
+          <t>Presencia de manchas de producto, suciedad o deterioro en el aislamiento térmico en {cantidad} zona(s) del circuito (longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1523,7 +1543,11 @@
           <t>cantidad, longitud, ubicacion</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -1642,7 +1666,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Par galvánico por incompatibilidad de materiales (bridas de acero inoxidable con espárragos y tuercas de acero al carbono) en {cantidad} uniones bridadas del circuito NPS {nps}.</t>
+          <t>Hallazgo: Par galvánico por incompatibilidad de materiales (bridas de acero inoxidable con espárragos y tuercas de acero al carbono) en {cantidad} unión(es) bridada(s) del circuito NPS {nps}.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1655,7 +1679,11 @@
           <t>cantidad, nps</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -1749,12 +1777,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Deterioro del recubrimiento y presencia de corrosión {severidad} en {cantidad} uniones bridadas, incluyendo sus elementos de ajuste (espárragos y tuercas) en la línea NPS {nps}.</t>
+          <t>Hallazgo: Deterioro del recubrimiento y presencia de corrosión {severidad} en {cantidad} unión(es) bridada(s), incluyendo sus elementos de ajuste (espárragos y tuercas) en la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} uniones bridadas, incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} unión(es) bridada(s), incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1764,7 +1792,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>severidad=leve a moderada</t>
+          <t>severidad=leve a moderada; cantidad=varias</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1814,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Deterioro del recubrimiento y corrosión moderada en bridas, con corrosión severa en espárragos y tuercas en {cantidad} uniones bridadas de NPS {nps}.</t>
+          <t>Hallazgo: Deterioro del recubrimiento y corrosión moderada en bridas, con corrosión severa en espárragos y tuercas en {cantidad} unión(es) bridada(s) de NPS {nps}.</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) en las {cantidad} uniones bridadas de NPS {nps}, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 y ASME B31.3; asimismo, efectuar el mantenimiento del recubrimiento en las bridas según los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) en {cantidad} unión(es) bridada(s) de NPS {nps}, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 y ASME B31.3; asimismo, efectuar el mantenimiento del recubrimiento en las bridas según los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1799,7 +1827,11 @@
           <t>cantidad, nps</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -1819,7 +1851,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Unión bridada de NPS {nps} con uso de pernos en lugar de espárragos de ajuste ({cantidad} unidades).</t>
+          <t>Hallazgo: Unión bridada de NPS {nps} con uso de {cantidad} perno(s) en lugar de espárragos de ajuste.</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1832,7 +1864,11 @@
           <t>nps, cantidad</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -1865,7 +1901,11 @@
           <t>cantidad, nps</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varios</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2195,70 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VALVULA_MANCHA_PRODUCTO_SOLIDIFICADO</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mancha de producto solidificado y deterioro de recubrimiento en válvula</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Deterioro del recubrimiento (pintura) y mancha de producto solidificado en válvula de {tipo} de NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento del recubrimiento en la válvula de {tipo} de NPS {nps}, incluyendo el retiro del producto solidificado como parte de la preparación de superficie, conforme al esquema de pinturas PE-B-0600.01-I y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VALVULA_AUSENCIA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ausencia de niple y tapón roscado en válvula</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ausencia de niple y tapón roscado en la válvula de {tipo} de NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Instalar de forma inmediata el niple y el tapón roscado faltantes en la válvula de {tipo} de NPS {nps}, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2207,7 +2271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4595,6 +4659,98 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>45</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VALVULA_MANCHA_PRODUCTO_SOLIDIFICADO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>mancha</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>45</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VALVULA_MANCHA_PRODUCTO_SOLIDIFICADO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>producto solidificado | solidificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>46</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VALVULA_AUSENCIA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>niple</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>46</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>VALVULA_AUSENCIA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>valvulas; válvulas</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>tapon | tapón</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2259,6 +2259,80 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TUBERIA_MODERADA_SEVERA_SIN_ESPESORES</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Corrosión moderada/severa en tramo corto (sin medición de espesores)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Corrosión {severidad} en un tramo de aproximadamente {longitud} metros, afectando a {elemento} de NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo de {elemento} de NPS {nps} afectado(s) por la corrosión, utilizando su respectivo WPS y PQR previamente calificado, conforme a ASME B31.3 y API 570.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>severidad, longitud, elemento, nps</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>severidad=moderada a severa; elemento=tubería y accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TUBERIA_ELEMENTO_AJENO_AMARRADO</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Elemento ajeno (cinta, alambre) amarrado a la línea inspeccionada</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Se identificó un elemento ajeno a la línea ({elemento}), amarrando la línea inspeccionada NPS {nps} a otra línea ubicada en paralelo.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Realizar el retiro del elemento ajeno a la línea inspeccionada ({elemento}) NPS {nps}, conforme a los procedimientos de mantenimiento Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>elemento, nps</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>elemento=elemento ajeno (cinta, alambre u otro)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2271,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3525,7 +3599,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>no cumple ninguna funcion | no cumple ninguna función | no comple ninguna funcion | no comple ninguna función | no corresponde a la linea | no corresponde a la línea | no corresponde a esta linea | no corresponde a esta línea | no pertenece a la linea | no pertenece a la línea | ajena a la linea | ajena a la línea | otro sistema</t>
+          <t>no cumple ninguna funcion | no cumple ninguna función | no comple ninguna funcion | no comple ninguna función | no corresponde a la linea | no corresponde a la línea | no corresponde a esta linea | no corresponde a esta línea | no pertenece a la linea | no pertenece a la línea | ajena a la linea | ajena a la línea | otro sistema | linea ajena | línea ajena | otra linea | otra línea</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -4748,6 +4822,80 @@
       <c r="E103" t="inlineStr">
         <is>
           <t>tapon | tapón</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>47</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TUBERIA_MODERADA_SEVERA_SIN_ESPESORES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>moderada y severa | moderada a severa | severa y moderada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>medicion de espesores | medición de espesores | perdida de espesor | pérdida de espesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>48</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TUBERIA_ELEMENTO_AJENO_AMARRADO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>cinta de valizamiento | cinta señalizadora | alambre de amarre</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>48</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TUBERIA_ELEMENTO_AJENO_AMARRADO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>recubrimientos; componentes; placas orificio; puntos de inyecc; instrumentacion; instrumentación</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>amarrando | amarrada | atada | sujetando | sujeta</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2333,6 +2333,38 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SOPORTE_AMARRE_PROVISIONAL_ALAMBRE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Amarre provisional con alambre en lugar de abrazadera</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Se evidencia amarre provisional con alambre en lugar de una abrazadera adecuada para la sujeción de la tubería NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Retirar el amarre provisional (alambre) e instalar una abrazadera/soporte adecuado para la sujeción de la tubería NPS {nps}, conforme a la norma MSS SP-58 y los estándares Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2345,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3070,7 +3102,11 @@
           <t>abrazadera</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>amarre provisional | alambre de amarre</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -4896,6 +4932,52 @@
       <c r="E106" t="inlineStr">
         <is>
           <t>amarrando | amarrada | atada | sujetando | sujeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>49</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SOPORTE_AMARRE_PROVISIONAL_ALAMBRE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>amarre provisional | amarre</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>49</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SOPORTE_AMARRE_PROVISIONAL_ALAMBRE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>alambre</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento en la totalidad del recubrimiento (pintura) del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento en la totalidad del recubrimiento de {elemento} pertenecientes al circuito NPS {nps} (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1050,20 +1050,16 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Pérdida de la manivela / palanca de accionamiento en la válvula de {tipo} de NPS {nps}, de bloqueo y purga del indicador de presión manómetro.</t>
+          <t>Pérdida de la manivela / palanca de accionamiento en la válvula de aguja de regulación para manómetro.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de la manivela de la válvula de aguja de NPS {nps} para restablecer la maniobrabilidad del elemento de bloqueo y purga, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>tipo, nps</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr"/>
+          <t>Realizar el reemplazo de la manivela de la válvula de aguja para restablecer la maniobrabilidad del elemento de regulación y aislamiento, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento correctivo de la unión cuerpo-bonete y reemplazo del empaque/junta en la válvula de control {tag} / NPS {nps}, así como la limpieza integral del producto acumulado, siguiendo los lineamientos del código API 570 y los estándares Repsol aplicables.</t>
+          <t>Realizar el mantenimiento correctivo de la unión cuerpo-bonete y reemplazo del empaque/junta en la válvula de control {tag} / NPS {nps}, así como la limpieza integral del producto acumulado, siguiendo los lineamientos del código API 570 y los estándares Repsol aplicables. (Nota: se aplica API 570 por tratarse de un componente activo de tubería en servicio).</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1535,12 +1531,12 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {cantidad} zona(s) afectada(s) del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>cantidad, longitud, ubicacion</t>
+          <t>cantidad, longitud</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento correctivo de la unión cuerpo-bonete y reemplazo del empaque/junta en la válvula de control {tag} / NPS {nps}, así como la limpieza integral del producto acumulado, siguiendo los lineamientos del código API 570 y los estándares Repsol aplicables. (Nota: se aplica API 570 por tratarse de un componente activo de tubería en servicio).</t>
+          <t>Realizar el mantenimiento correctivo de la unión cuerpo-bonete y reemplazo del empaque/junta en la válvula de control {tag} / NPS {nps}, así como la limpieza integral del producto acumulado, siguiendo los lineamientos del código API 570 y los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Corrosión {severidad} y pérdida de espesor (verificado con medición de espesores) en tuberías y accesorios ({elemento}) (longitud aprox. {longitud} metros).</t>
+          <t>Corrosión severa y pérdida de espesor (verificado con medición de espesores) en tuberías y accesorios ({elemento}) (longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>severidad, elemento, longitud, nps, schedule, material</t>
+          <t>elemento, longitud, nps, schedule, material</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>severidad=moderada; elemento=tubería/accesorio</t>
+          <t>elemento=tubería/accesorio</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Presencia de corrosión (otros) en tramo no accesible: circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
+          <t>Circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3. (Nota: al ser corrosión severa, se excluye el mantenimiento rutinario de recubrimiento).</t>
+          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo del soporte y de {cantidad} abrazadera(s) en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58. (Sin mantenimiento de recubrimiento/pintura).</t>
+          <t>Realizar el reemplazo del soporte y de {cantidad} abrazadera(s) en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58.</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo spring hanger de la línea NPS {nps}, conforme a los estándares Repsol ED-B-06.00-04d y al documento técnico PE-B-0600.01H00R05. (No se especifica código de color de acabado por sus consideraciones especiales frente a otros soportes).</t>
+          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo spring hanger de la línea NPS {nps}, conforme a los estándares Repsol ED-B-06.00-04d y al documento técnico PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Contaminación del aislamiento térmico (humedad), así como también se visualiza corrosión moderada en zonas con ventanas de inspección (línea NPS {nps}).</t>
+          <t>Contaminación del aislamiento térmico (humedad), así como también se visualiza corrosión moderada en zonas con ventanas de inspección.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1435,11 +1435,7 @@
           <t>Retirar el aislamiento térmico y efectuar la limpieza de la zona corroída para evaluar el grado de daño. En caso de verificarse corrosión superficial, aplicar recubrimiento de pintura, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05. Nota: solo se aplica recubrimiento a tuberías con temperatura de operación menor o igual a 200 °C.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>nps</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1847,7 +1843,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Unión bridada de NPS {nps} con uso de {cantidad} perno(s) en lugar de espárragos de ajuste.</t>
+          <t>Hallazgo: Unión bridada de NPS {nps} con uso de pernos en lugar de espárragos de ajuste ({cantidad} unidad(es)).</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Corrosión {severidad} y pérdida de espesor (verificado con medición de espesores) en tuberías y accesorios ({elemento}) (longitud aprox. {longitud} metros).</t>
+          <t>Corrosión severa y pérdida de espesor (verificado con medición de espesores) en tuberías y accesorios ({elemento}) (longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>severidad, elemento, longitud, nps, schedule, material</t>
+          <t>elemento, longitud, nps, schedule, material</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>severidad=moderada; elemento=tubería/accesorio</t>
+          <t>elemento=tubería/accesorio</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el mantenimiento en la totalidad del recubrimiento (pintura) del circuito NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
+          <t>Efectuar el mantenimiento en la totalidad del recubrimiento de {elemento} pertenecientes al circuito NPS {nps} (longitud aprox. {longitud} metros), siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Presencia de corrosión (otros) en tramo no accesible: circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
+          <t>Circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3. (Nota: al ser corrosión severa, se excluye el mantenimiento rutinario de recubrimiento).</t>
+          <t>Realizar el reemplazo de los pernos de ajuste (del volante y de la prensaestopas) y el mantenimiento correctivo de los mecanismos (volante, bonete y prensaestopas) con su respectiva lubricación en {cantidad} válvula(s) de {tipo} de NPS {nps}, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1050,20 +1050,16 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Pérdida de la manivela / palanca de accionamiento en la válvula de {tipo} de NPS {nps}, de bloqueo y purga del indicador de presión manómetro.</t>
+          <t>Pérdida de la manivela / palanca de accionamiento en la válvula de aguja de regulación para manómetro.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de la manivela de la válvula de aguja de NPS {nps} para restablecer la maniobrabilidad del elemento de bloqueo y purga, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>tipo, nps</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr"/>
+          <t>Realizar el reemplazo de la manivela de la válvula de aguja para restablecer la maniobrabilidad del elemento de regulación y aislamiento, conforme a los lineamientos de la norma API 598 y el código ASME B31.3.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo del soporte y de {cantidad} abrazadera(s) en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58. (Sin mantenimiento de recubrimiento/pintura).</t>
+          <t>Realizar el reemplazo del soporte y de {cantidad} abrazadera(s) en el tramo de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58.</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1403,7 +1399,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo spring hanger de la línea NPS {nps}, conforme a los estándares Repsol ED-B-06.00-04d y al documento técnico PE-B-0600.01H00R05. (No se especifica código de color de acabado por sus consideraciones especiales frente a otros soportes).</t>
+          <t>Realizar el mantenimiento del recubrimiento en el soporte tipo spring hanger de la línea NPS {nps}, conforme a los estándares Repsol ED-B-06.00-04d y al documento técnico PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1431,7 +1427,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Contaminación del aislamiento térmico (humedad), así como también se visualiza corrosión moderada en zonas con ventanas de inspección (línea NPS {nps}).</t>
+          <t>Contaminación del aislamiento térmico (humedad), así como también se visualiza corrosión moderada en zonas con ventanas de inspección.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1439,11 +1435,7 @@
           <t>Retirar el aislamiento térmico y efectuar la limpieza de la zona corroída para evaluar el grado de daño. En caso de verificarse corrosión superficial, aplicar recubrimiento de pintura, siguiendo los estándares Repsol ED-B-06.00-04d y el documento PE-B-0600.01H00R05. Nota: solo se aplica recubrimiento a tuberías con temperatura de operación menor o igual a 200 °C.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>nps</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1535,12 +1527,12 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {cantidad} zona(s) afectada(s) del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>cantidad, longitud, ubicacion</t>
+          <t>cantidad, longitud</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -1851,7 +1843,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Unión bridada de NPS {nps} con uso de {cantidad} perno(s) en lugar de espárragos de ajuste.</t>
+          <t>Hallazgo: Unión bridada de NPS {nps} con uso de pernos en lugar de espárragos de ajuste ({cantidad} unidad(es)).</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
+          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, mediante proceso GTAW con material de aporte ER-70S-6, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -2354,6 +2354,538 @@
       <c r="F49" t="inlineStr">
         <is>
           <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>INDICADOR_TEMPERATURA_DETERIORADO</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Indicador de temperatura deteriorado</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Deterioro del indicador de temperatura {tag} de la línea, afectando la confiabilidad de la lectura del sistema.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo del indicador de temperatura {tag} asociado a la línea, asegurando compatibilidad con el rango operativo del sistema y siguiendo los procedimientos de instrumentación establecidos.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>INSTRUMENTO_NIPLE_UNION_UNIVERSAL_CORROSION</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Corrosión en niple y unión universal de instrumento</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Corrosión {severidad} en el niple y la unión universal de NPS {nps} del instrumento {tag}, con deterioro del recubrimiento en el cabezal.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo del niple y la unión universal de NPS {nps} del instrumento {tag}, así como el mantenimiento del recubrimiento del cabezal, a fin de prevenir riesgos asociados a la corrosión y asegurar el correcto funcionamiento del sistema, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>severidad, nps, tag</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>severidad=moderada</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VALVULA_REEMPLAZO_TOTAL_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Reemplazo total de válvula por corrosión severa generalizada</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Corrosión severa generalizada en la válvula de {tipo} de NPS {nps}, comprometiendo su integridad estructural.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Reemplazar totalmente la válvula de {tipo} de NPS {nps} debido a la corrosión severa observada, en cumplimiento con los criterios de inspección de piezas de válvula de la práctica recomendada API 621, sección 6.2.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TUBERIA_VIBRACION_SOPORTES_INSUFICIENTES</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Vibración por posible ausencia de soportes</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Se evidencia vibración en el tramo de tubería cerca de {ubicacion}, por posible ausencia de soportes, pudiendo generar fatiga mecánica inducida por la vibración.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Instalar soportes adecuados en el tramo de tubería cerca de {ubicacion} para evitar esfuerzos inaceptables por vibración, proteger la integridad del sistema y minimizar el riesgo de daño por fatiga o desplazamiento, conforme a la práctica recomendada API 574, sección 4.7.2, y API 571, sección 3.43.a).</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TUBERIA_TAPON_DRENAJE_AUSENTE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ausencia de tapón en niple de drenaje</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ausencia de tapón en el niple de drenaje de NPS {nps}, cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Instalar un tapón en el niple de drenaje de NPS {nps} cerca de {ubicacion}, con el fin de evitar fugas y mantener la integridad del sistema.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>nps, ubicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fuga en drenaje entre niple y tapón</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fuga de producto en forma de goteo en el niple y la unión roscada del drenaje de NPS {nps}, con acumulación de producto en la zona.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento preventivo de la válvula de drenaje de NPS {nps} y de la unión roscada entre el tapón y el niple, incluyendo pruebas de apertura y cierre para asegurar su correcto funcionamiento y un sello eficaz, conforme al estándar API 570, sección 7.12.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Corrosión en bulón de anclaje de soporte</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Corrosión {severidad} en el bulón de anclaje del soporte cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento o el reemplazo del bulón de anclaje del soporte cerca de {ubicacion}, conforme a los procedimientos y estándares Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>severidad, ubicacion</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>severidad=moderada a severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SOPORTE_BASE_CONCRETO_AGRIETADA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Agrietamiento en base de concreto de soporte</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Agrietamiento y/o desprendimiento de segmentos en la base de concreto del soporte cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Realizar la reparación de la base de concreto del soporte cerca de {ubicacion}, asegurando el resane de las grietas que puedan canalizar humedad hacia la estructura metálica interna, conforme a los lineamientos del estándar Repsol ED-Q-01.00-03.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BRIDA_MONTAJE_PARALELISMO_INCORRECTO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Falta de paralelismo en montaje de unión bridada</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Se evidencia falta de paralelismo en el montaje de la unión bridada de NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Corregir el montaje de la unión bridada de NPS {nps} conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006, garantizando que la tolerancia de paralelismo (PRL) no exceda 1 mm entre el punto más cercano y el más lejano a lo largo de la superficie de sellado.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CONTACTO_DIRECTO_SIN_AISLANTE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Contacto directo genérico soporte-tubería sin material aislante</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Contacto directo de la tubería NPS {nps} con {cantidad} soporte(s) metálico(s), sin ningún tipo de material aislante, constituyendo un punto de contacto conforme a la norma API 570, sección 3.1.11.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Instalar material de protección (teflón, elastómero o neopreno) en la zona de contacto entre la tubería NPS {nps} y {cantidad} soporte(s) metálico(s), para evitar el contacto directo metal-metal, de acuerdo con la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a (sección 5.5).</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>nps, cantidad</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cantidad=varios</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TUBERIA_INSPECCION_LIMITADA_POR_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Inspección limitada por presencia de aislamiento térmico</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>El circuito NPS {nps} cuenta con aislamiento térmico, lo cual impide su inspección visual directa.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Inspeccionar la línea NPS {nps} con aislamiento térmico mediante termografía infrarroja, medición puntual de espesores (PEC) y radiografía de perfil, conforme a la práctica recomendada API 574 y API 583, o, si no es posible, retirar el aislamiento para medir los espesores con ultrasonido conforme al código API 570.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VALVULA_VOLANTE_ORIENTACION_INCORRECTA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Volante orientado incorrectamente</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Se evidencia {cantidad} válvula(s) de {tipo} instalada(s) con el volante orientado hacia la parte inferior de la línea.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Si {cantidad} válvula(s) de {tipo} puede(n) ser reorientada(s) sin comprometer la operación del sistema, se recomienda instalar el volante en una posición horizontal o ligeramente inclinada hacia arriba, para evitar la acumulación de líquidos.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>cantidad, tipo</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>INDICADOR_PLACA_CALIBRACION_AUSENTE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ausencia de placa de identificación/calibración</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ausencia de placa de identificación y/o datos de calibración vigentes en {elemento}.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Instalar la placa de identificación con los datos de calibración vigentes en {elemento}, conforme a la práctica recomendada API 572, sección 10.2.3.8.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>elemento</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>elemento=el instrumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER_LIMPIEZA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Spring hanger con polución que limita su inspección</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Se evidencia acumulación de polución en el soporte tipo spring hanger, limitando su inspección visual.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Realizar la limpieza del soporte tipo spring hanger para retirar la polución acumulada y permitir su inspección visual completa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BRIDA_CORTE_SEGMENTO_INTERNO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Corte de segmento en cara interna de brida</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Se evidencia corte de un segmento en la cara interna de la brida de NPS {nps}, siendo rechazada conforme al estándar ASME PCC-1 (figura D-2-2, tabla D-3-1M).</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo de la brida de NPS {nps} que presenta corte en su cara interna, conforme al estándar ASME PCC-1 (figura D-2-2, tabla D-3-1M) y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_RETIRO_DETECCION_FUGA_CONDENSADO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Retiro de aislamiento para detectar fuga de condensado</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Presencia de humedad en el aislamiento térmico cerca de {ubicacion}, sin poder determinar con el aislamiento colocado el punto exacto de la fuga de condensado.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Realizar el retiro y reemplazo del aislamiento térmico cerca de {ubicacion} debido a la presencia de humedad; durante el retiro, identificar con precisión el punto de fuga de condensado y realizar la reparación correspondiente.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3218,7 +3750,11 @@
           <t>ausencia | ausente | falta de soporte | sin soporte | carece de soporte</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>vibracion | vibración</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -3290,7 +3826,7 @@
           <t>corrosion | corrosión</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -3316,7 +3852,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>severa | spring hanger | u-bolt | u bolt | ubolt</t>
+          <t>severa | spring hanger | u-bolt | u bolt | ubolt | bulon de anclaje | bulón de anclaje</t>
         </is>
       </c>
     </row>
@@ -4829,6 +5365,11 @@
           <t>niple</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>fuga | goteo</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4970,6 +5511,642 @@
       <c r="E108" t="inlineStr">
         <is>
           <t>alambre</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>50</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>INDICADOR_TEMPERATURA_DETERIORADO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>indicador de temperatura | termometro | termómetro | TI-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>51</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>INSTRUMENTO_NIPLE_UNION_UNIVERSAL_CORROSION</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>union universal | unión universal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>52</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VALVULA_REEMPLAZO_TOTAL_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>corrosion severa | corrosión severa</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>pernos</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>52</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VALVULA_REEMPLAZO_TOTAL_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>generalizada | en toda la valvula | en toda la válvula</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>53</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TUBERIA_VIBRACION_SOPORTES_INSUFICIENTES</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>componentes; soportes</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>vibracion | vibración</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>54</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TUBERIA_TAPON_DRENAJE_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>componentes; valvulas</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ausencia de tapon | ausencia de tapón | sin tapon | sin tapón | no cuenta con tapon | no cuenta con tapón</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>54</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TUBERIA_TAPON_DRENAJE_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>componentes; valvulas</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>drenaje | niple</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>55</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>valvulas; componentes</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>fuga | goteo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>55</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>valvulas; componentes</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>drenaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>55</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>valvulas; componentes</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>niple | tapon | tapón</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>56</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>bulon de anclaje | bulón de anclaje | perno de anclaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>57</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SOPORTE_BASE_CONCRETO_AGRIETADA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>base de concreto | base concreto</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>57</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SOPORTE_BASE_CONCRETO_AGRIETADA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>agrieta | rajadura | grieta | desprendimiento de segmentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>58</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BRIDA_MONTAJE_PARALELISMO_INCORRECTO</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>paralelismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>59</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CONTACTO_DIRECTO_SIN_AISLANTE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>contacto directo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>u-bolt | u bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>59</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CONTACTO_DIRECTO_SIN_AISLANTE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>sin material aislante | sin aislante | sin ningun tipo de material aislante | sin ningún tipo de material aislante | carecen de material aislante | carecen de aislante</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>60</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TUBERIA_INSPECCION_LIMITADA_POR_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>aislamiento; componentes; recubrimientos</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>impide su inspeccion | impide su inspección | impide la inspeccion | impide la inspección</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>60</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TUBERIA_INSPECCION_LIMITADA_POR_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>aislamiento; componentes; recubrimientos</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>61</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>VALVULA_VOLANTE_ORIENTACION_INCORRECTA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>volante</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>desprendid | suelto | perdida | pérdida | rotura | ausencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>61</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>VALVULA_VOLANTE_ORIENTACION_INCORRECTA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>orientad | orientacion | orientación | parte inferior de la linea | parte inferior de la línea</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>62</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>INDICADOR_PLACA_CALIBRACION_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores; valvulas</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>placa de calibracion | placa de calibración | placa de identificacion | placa de identificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>62</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>INDICADOR_PLACA_CALIBRACION_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores; valvulas</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ausencia | sin placa | no cuenta con placa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>63</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER_LIMPIEZA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>spring hanger</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>63</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER_LIMPIEZA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>polucion | polución | limitando su inspeccion | limitando su inspección | limita la inspeccion | limita la inspección</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>64</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BRIDA_CORTE_SEGMENTO_INTERNO</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>bridas; placas orificio</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>corte de un segmento | corte en la parte interna | segmento interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>65</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_RETIRO_DETECCION_FUGA_CONDENSADO</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>fuga de condensado | punto de fuga</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>65</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_RETIRO_DETECCION_FUGA_CONDENSADO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>humedad</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, mediante proceso GTAW con material de aporte ER-70S-6, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
+          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2357,6 +2357,538 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>INDICADOR_TEMPERATURA_DETERIORADO</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Indicador de temperatura deteriorado</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Deterioro del indicador de temperatura {tag} de la línea, afectando la confiabilidad de la lectura del sistema.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo del indicador de temperatura {tag} asociado a la línea, asegurando compatibilidad con el rango operativo del sistema y siguiendo los procedimientos de instrumentación establecidos.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>INSTRUMENTO_NIPLE_UNION_UNIVERSAL_CORROSION</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Corrosión en niple y unión universal de instrumento</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Corrosión {severidad} en el niple y la unión universal de NPS {nps} del instrumento {tag}, con deterioro del recubrimiento en el cabezal.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo del niple y la unión universal de NPS {nps} del instrumento {tag}, así como el mantenimiento del recubrimiento del cabezal, a fin de prevenir riesgos asociados a la corrosión y asegurar el correcto funcionamiento del sistema, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>severidad, nps, tag</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>severidad=moderada</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VALVULA_REEMPLAZO_TOTAL_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Reemplazo total de válvula por corrosión severa generalizada</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Corrosión severa generalizada en la válvula de {tipo} de NPS {nps}, comprometiendo su integridad estructural.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Reemplazar totalmente la válvula de {tipo} de NPS {nps} debido a la corrosión severa observada, en cumplimiento con los criterios de inspección de piezas de válvula de la práctica recomendada API 621, sección 6.2.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TUBERIA_VIBRACION_SOPORTES_INSUFICIENTES</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Vibración por posible ausencia de soportes</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Se evidencia vibración en el tramo de tubería cerca de {ubicacion}, por posible ausencia de soportes, pudiendo generar fatiga mecánica inducida por la vibración.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Instalar soportes adecuados en el tramo de tubería cerca de {ubicacion} para evitar esfuerzos inaceptables por vibración, proteger la integridad del sistema y minimizar el riesgo de daño por fatiga o desplazamiento, conforme a la práctica recomendada API 574, sección 4.7.2, y API 571, sección 3.43.a).</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TUBERIA_TAPON_DRENAJE_AUSENTE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ausencia de tapón en niple de drenaje</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ausencia de tapón en el niple de drenaje de NPS {nps}, cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Instalar un tapón en el niple de drenaje de NPS {nps} cerca de {ubicacion}, con el fin de evitar fugas y mantener la integridad del sistema.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>nps, ubicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fuga en drenaje entre niple y tapón</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fuga de producto en forma de goteo en el niple y la unión roscada del drenaje de NPS {nps}, con acumulación de producto en la zona.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento preventivo de la válvula de drenaje de NPS {nps} y de la unión roscada entre el tapón y el niple, incluyendo pruebas de apertura y cierre para asegurar su correcto funcionamiento y un sello eficaz, conforme al estándar API 570, sección 7.12.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Corrosión en bulón de anclaje de soporte</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Corrosión {severidad} en el bulón de anclaje del soporte cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Realizar el mantenimiento o el reemplazo del bulón de anclaje del soporte cerca de {ubicacion}, conforme a los procedimientos y estándares Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>severidad, ubicacion</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>severidad=moderada a severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SOPORTE_BASE_CONCRETO_AGRIETADA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Agrietamiento en base de concreto de soporte</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Agrietamiento y/o desprendimiento de segmentos en la base de concreto del soporte cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Realizar la reparación de la base de concreto del soporte cerca de {ubicacion}, asegurando el resane de las grietas que puedan canalizar humedad hacia la estructura metálica interna, conforme a los lineamientos del estándar Repsol ED-Q-01.00-03.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BRIDA_MONTAJE_PARALELISMO_INCORRECTO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Falta de paralelismo en montaje de unión bridada</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Se evidencia falta de paralelismo en el montaje de la unión bridada de NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Corregir el montaje de la unión bridada de NPS {nps} conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006, garantizando que la tolerancia de paralelismo (PRL) no exceda 1 mm entre el punto más cercano y el más lejano a lo largo de la superficie de sellado.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CONTACTO_DIRECTO_SIN_AISLANTE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Contacto directo genérico soporte-tubería sin material aislante</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Contacto directo de la tubería NPS {nps} con {cantidad} soporte(s) metálico(s), sin ningún tipo de material aislante, constituyendo un punto de contacto conforme a la norma API 570, sección 3.1.11.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Instalar material de protección (teflón, elastómero o neopreno) en la zona de contacto entre la tubería NPS {nps} y {cantidad} soporte(s) metálico(s), para evitar el contacto directo metal-metal, de acuerdo con la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a (sección 5.5).</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>nps, cantidad</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cantidad=varios</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TUBERIA_INSPECCION_LIMITADA_POR_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TUBERIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Inspección limitada por presencia de aislamiento térmico</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>El circuito NPS {nps} cuenta con aislamiento térmico, lo cual impide su inspección visual directa.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Inspeccionar la línea NPS {nps} con aislamiento térmico mediante termografía infrarroja, medición puntual de espesores (PEC) y radiografía de perfil, conforme a la práctica recomendada API 574 y API 583, o, si no es posible, retirar el aislamiento para medir los espesores con ultrasonido conforme al código API 570.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VALVULA_VOLANTE_ORIENTACION_INCORRECTA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>VALVULA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Volante orientado incorrectamente</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Se evidencia {cantidad} válvula(s) de {tipo} instalada(s) con el volante orientado hacia la parte inferior de la línea.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Si {cantidad} válvula(s) de {tipo} puede(n) ser reorientada(s) sin comprometer la operación del sistema, se recomienda instalar el volante en una posición horizontal o ligeramente inclinada hacia arriba, para evitar la acumulación de líquidos.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>cantidad, tipo</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>INDICADOR_PLACA_CALIBRACION_AUSENTE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ausencia de placa de identificación/calibración</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ausencia de placa de identificación y/o datos de calibración vigentes en {elemento}.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Instalar la placa de identificación con los datos de calibración vigentes en {elemento}, conforme a la práctica recomendada API 572, sección 10.2.3.8.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>elemento</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>elemento=el instrumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER_LIMPIEZA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Spring hanger con polución que limita su inspección</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Se evidencia acumulación de polución en el soporte tipo spring hanger, limitando su inspección visual.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Realizar la limpieza del soporte tipo spring hanger para retirar la polución acumulada y permitir su inspección visual completa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BRIDA_CORTE_SEGMENTO_INTERNO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Corte de segmento en cara interna de brida</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Se evidencia corte de un segmento en la cara interna de la brida de NPS {nps}, siendo rechazada conforme al estándar ASME PCC-1 (figura D-2-2, tabla D-3-1M).</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo de la brida de NPS {nps} que presenta corte en su cara interna, conforme al estándar ASME PCC-1 (figura D-2-2, tabla D-3-1M) y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_RETIRO_DETECCION_FUGA_CONDENSADO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Retiro de aislamiento para detectar fuga de condensado</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Presencia de humedad en el aislamiento térmico cerca de {ubicacion}, sin poder determinar con el aislamiento colocado el punto exacto de la fuga de condensado.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Realizar el retiro y reemplazo del aislamiento térmico cerca de {ubicacion} debido a la presencia de humedad; durante el retiro, identificar con precisión el punto de fuga de condensado y realizar la reparación correspondiente.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2369,7 +2901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3218,7 +3750,11 @@
           <t>ausencia | ausente | falta de soporte | sin soporte | carece de soporte</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>vibracion | vibración</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -3290,7 +3826,7 @@
           <t>corrosion | corrosión</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -3316,7 +3852,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>severa | spring hanger | u-bolt | u bolt | ubolt</t>
+          <t>severa | spring hanger | u-bolt | u bolt | ubolt | bulon de anclaje | bulón de anclaje</t>
         </is>
       </c>
     </row>
@@ -4829,6 +5365,11 @@
           <t>niple</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>fuga | goteo</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4970,6 +5511,642 @@
       <c r="E108" t="inlineStr">
         <is>
           <t>alambre</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>50</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>INDICADOR_TEMPERATURA_DETERIORADO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>indicador de temperatura | termometro | termómetro | TI-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>51</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>INSTRUMENTO_NIPLE_UNION_UNIVERSAL_CORROSION</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>union universal | unión universal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>52</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VALVULA_REEMPLAZO_TOTAL_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>corrosion severa | corrosión severa</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>pernos</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>52</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VALVULA_REEMPLAZO_TOTAL_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>generalizada | en toda la valvula | en toda la válvula</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>53</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TUBERIA_VIBRACION_SOPORTES_INSUFICIENTES</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>componentes; soportes</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>vibracion | vibración</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>54</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TUBERIA_TAPON_DRENAJE_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>componentes; valvulas</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ausencia de tapon | ausencia de tapón | sin tapon | sin tapón | no cuenta con tapon | no cuenta con tapón</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>54</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TUBERIA_TAPON_DRENAJE_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>componentes; valvulas</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>drenaje | niple</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>55</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>valvulas; componentes</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>fuga | goteo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>55</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>valvulas; componentes</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>drenaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>55</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VALVULA_DRENAJE_FUGA_NIPLE_TAPON</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>valvulas; componentes</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>niple | tapon | tapón</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>56</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>bulon de anclaje | bulón de anclaje | perno de anclaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>57</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SOPORTE_BASE_CONCRETO_AGRIETADA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>base de concreto | base concreto</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>57</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SOPORTE_BASE_CONCRETO_AGRIETADA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>agrieta | rajadura | grieta | desprendimiento de segmentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>58</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BRIDA_MONTAJE_PARALELISMO_INCORRECTO</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>paralelismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>59</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CONTACTO_DIRECTO_SIN_AISLANTE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>contacto directo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>u-bolt | u bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>59</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CONTACTO_DIRECTO_SIN_AISLANTE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>sin material aislante | sin aislante | sin ningun tipo de material aislante | sin ningún tipo de material aislante | carecen de material aislante | carecen de aislante</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>60</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TUBERIA_INSPECCION_LIMITADA_POR_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>aislamiento; componentes; recubrimientos</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>impide su inspeccion | impide su inspección | impide la inspeccion | impide la inspección</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>60</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TUBERIA_INSPECCION_LIMITADA_POR_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>aislamiento; componentes; recubrimientos</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>61</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>VALVULA_VOLANTE_ORIENTACION_INCORRECTA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>volante</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>desprendid | suelto | perdida | pérdida | rotura | ausencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>61</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>VALVULA_VOLANTE_ORIENTACION_INCORRECTA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>valvulas</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>orientad | orientacion | orientación | parte inferior de la linea | parte inferior de la línea</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>62</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>INDICADOR_PLACA_CALIBRACION_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores; valvulas</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>placa de calibracion | placa de calibración | placa de identificacion | placa de identificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>62</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>INDICADOR_PLACA_CALIBRACION_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>instrumentacion; instrumentación; indicadores; valvulas</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ausencia | sin placa | no cuenta con placa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>63</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER_LIMPIEZA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>spring hanger</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>63</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SOPORTE_SPRING_HANGER_LIMPIEZA_INSPECCION</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>polucion | polución | limitando su inspeccion | limitando su inspección | limita la inspeccion | limita la inspección</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>64</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BRIDA_CORTE_SEGMENTO_INTERNO</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>bridas; placas orificio</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>corte de un segmento | corte en la parte interna | segmento interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>65</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_RETIRO_DETECCION_FUGA_CONDENSADO</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>fuga de condensado | punto de fuga</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>65</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_RETIRO_DETECCION_FUGA_CONDENSADO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>humedad</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Efectuar el reemplazo de un (niple/tubería/accesorio) de NPS {nps}, Sch {schedule}, material {material}, utilizando su respectivo WPS y PQR previamente calificado.</t>
+          <t>Efectuar el reemplazo de un (niple/tubería/accesorio) de NPS {nps}, Sch {schedule}, material {material}, en una longitud aprox. de {longitud} metros, utilizando su respectivo WPS y PQR previamente calificado.</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Reparar el aislamiento térmico en {ubicacion} del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Reparar el aislamiento térmico en {ubicacion} del circuito NPS {nps}, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {cantidad} zona(s) afectada(s) del circuito, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Realizar limpieza y/o reemplazo del aislamiento térmico en {cantidad} zona(s) afectada(s) del circuito (longitud aprox. {longitud} metros), siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Reemplazar los espárragos por unos de longitud adecuada que garanticen sobresalir al menos dos (2) hilos de rosca por encima de la cara exterior de la tuerca, conforme a la norma ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Reemplazar los espárragos de la unión bridada de NPS {nps} por unos de longitud adecuada que garanticen sobresalir al menos dos (2) hilos de rosca por encima de la cara exterior de la tuerca, conforme a la norma ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de la totalidad de los elementos de ajuste de acero al carbono por espárragos y tuercas de acero inoxidable de grado compatible, conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
+          <t>Realizar el reemplazo de la totalidad de los elementos de ajuste de acero al carbono por espárragos y tuercas de acero inoxidable de grado compatible en {cantidad} unión(es) bridada(s) del circuito NPS {nps}, conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento de los elementos de ajuste de acero al carbono (espárragos y tuercas) en {cantidad} unión(es) bridada(s) afectada(s), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar el mantenimiento de los {cantidad_elementos} elementos de ajuste de acero al carbono (espárragos y tuercas) por cada una de las {cantidad} unión(es) bridada(s) afectada(s) del circuito NPS {nps}, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de los elementos de ajuste (espárragos y tuercas) de acero al carbono por elementos nuevos del mismo material, en {cantidad} unión(es) bridada(s) afectada(s), conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
+          <t>Realizar el reemplazo de los {cantidad_elementos} elementos de ajuste (espárragos y tuercas) de acero al carbono por elementos nuevos del mismo material, en {cantidad} unión(es) bridada(s) afectada(s) del circuito NPS {nps}, conforme a la norma ASME B31.3 y estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} unión(es) bridada(s), incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} unión(es) bridada(s) de NPS {nps}, incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Reemplazar los pernos por espárragos con tuercas en la unión bridada NPS {nps}, garantizando que sobresalgan al menos dos (2) hilos de rosca, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Reemplazar {cantidad} perno(s) por espárragos con tuercas en la unión bridada NPS {nps}, garantizando que sobresalgan al menos dos (2) hilos de rosca, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Instalar la tuerca hexagonal faltante en el espárrago de la junta bridada de NPS {nps} y aplicar apriete/torque verificado para garantizar un sellado uniforme, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Instalar {cantidad} tuerca(s) hexagonal(es) faltante(s) en los espárragos de la junta bridada de NPS {nps} y aplicar apriete/torque verificado para garantizar un sellado uniforme, conforme a ASME B31.3 y el procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Realizar el retiro y reubicación del soporte que está sujetado a la línea inspeccionada mediante la abrazadera tipo {tipo}, de acuerdo a los procedimientos Repsol aplicables.</t>
+          <t>Realizar el retiro y reubicación del soporte que está sujetado a la línea inspeccionada NPS {nps} mediante la abrazadera tipo {tipo}, de acuerdo a los procedimientos Repsol aplicables.</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Realizar el reemplazo de {elemento} de NPS {nps} afectado(s) por la corrosión, utilizando su respectivo WPS y PQR previamente calificado, conforme a ASME B31.3 y API 570.</t>
+          <t>Realizar el reemplazo de {elemento} de NPS {nps} afectado(s) por la corrosión en un tramo de aproximadamente {longitud} metros, utilizando su respectivo WPS y PQR previamente calificado, conforme a ASME B31.3 y API 570.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3554,7 +3554,11 @@
           <t>perdida | pérdida | perdido | rotura | rota</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>corrosion severa | corrosión severa</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -5607,7 +5611,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>generalizada | en toda la valvula | en toda la válvula</t>
+          <t>generalizada | en toda la valvula | en toda la válvula | perdida de material | pérdida de material | perdida de volante | pérdida de volante | perdida, rotura de la volante</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -3606,7 +3606,11 @@
           <t>ausencia | ausente | sin volante</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>perdida | pérdida | perdido | rotura | rota</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Realizar la reparación de la protección ignífuga en {elemento}, asegurando el resane de las grietas, conforme a los lineamientos de los estándares Repsol aplicables.</t>
+          <t>Realizar la reparación de la protección ignífuga en {elemento}, en la zona cercana a {ubicacion}, asegurando el resane de las grietas, conforme a los lineamientos de los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Se recomienda la corrección de la instalación de la abrazadera con respecto a la tubería NPS {nps}, de acuerdo a los procedimientos Repsol aplicables.</t>
+          <t>Se recomienda la corrección de la instalación de la abrazadera ubicada en {ubicacion} de la tubería NPS {nps}, de acuerdo a los procedimientos Repsol aplicables.</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>fuga | goteo</t>
+          <t>drenaje</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Realizar la reparación de la protección ignífuga en {elemento}, asegurando el resane de las grietas, conforme a los lineamientos de los estándares Repsol aplicables.</t>
+          <t>Realizar la reparación de la protección ignífuga en {elemento}, en la zona cercana a {ubicacion}, asegurando el resane de las grietas, conforme a los lineamientos de los estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Se recomienda la corrección de la instalación de la abrazadera con respecto a la tubería NPS {nps}, de acuerdo a los procedimientos Repsol aplicables.</t>
+          <t>Se recomienda la corrección de la instalación de la abrazadera ubicada en {ubicacion} de la tubería NPS {nps}, de acuerdo a los procedimientos Repsol aplicables.</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3606,7 +3606,11 @@
           <t>ausencia | ausente | sin volante</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>perdida | pérdida | perdido | rotura | rota</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -5371,7 +5375,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>fuga | goteo</t>
+          <t>drenaje</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1489,20 +1489,24 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de aislamiento térmico en {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros).</t>
+          <t>Ausencia de aislamiento térmico en {cantidad} sector(es)/tramo(s) de {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros).</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Instalar aislamiento térmico en {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros), siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Instalar aislamiento térmico en {cantidad} sector(es)/tramo(s) de {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros), siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>ubicacion, nps, longitud</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
+          <t>cantidad, ubicacion, nps, longitud</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varios</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
@@ -1625,20 +1629,24 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Hallazgo: Longitud insuficiente de espárragos en unión bridada de NPS {nps} (no sobresalen de la cara exterior de la tuerca).</t>
+          <t>Hallazgo: Longitud insuficiente en {cantidad} espárrago(s) en unión bridada de NPS {nps}, sin sobresalir de la cara exterior de la tuerca.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Reemplazar los espárragos de la unión bridada de NPS {nps} por unos de longitud adecuada que garanticen sobresalir al menos dos (2) hilos de rosca por encima de la cara exterior de la tuerca, conforme a la norma ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+          <t>Reemplazar {cantidad} espárrago(s) de la unión bridada de NPS {nps} por unos de longitud adecuada que garanticen sobresalir al menos dos (2) hilos de rosca por encima de la cara exterior de la tuerca, conforme a la norma ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>nps</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
+          <t>cantidad, nps</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varios</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -2020,22 +2028,22 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de soporte en {ubicacion} de la línea NPS {nps}.</t>
+          <t>Ausencia de {cantidad} soporte(s) en {ubicacion} de la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Realizar la instalación de un soporte en {ubicacion} de la línea NPS {nps}, conforme a los procedimientos específicos y estándares Repsol aplicables (ED-L-06.00-05a, sección 5.5, y la norma MSS SP-58).</t>
+          <t>Realizar la instalación de {cantidad} soporte(s) en {ubicacion} de la línea NPS {nps}, conforme a los procedimientos específicos y estándares Repsol aplicables (ED-L-06.00-05a, sección 5.5, y la norma MSS SP-58).</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>ubicacion, nps</t>
+          <t>cantidad, ubicacion, nps</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>ubicacion=el tramo observado</t>
+          <t>cantidad=varios</t>
         </is>
       </c>
     </row>
@@ -2094,22 +2102,22 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Ausencia de abrazadera tipo {tipo} en la línea NPS {nps}.</t>
+          <t>Ausencia de {cantidad} abrazadera(s) tipo {tipo} en la línea NPS {nps}.</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Realizar la instalación de una abrazadera tipo {tipo} en la línea NPS {nps}, conforme a la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a.</t>
+          <t>Realizar la instalación de {cantidad} abrazadera(s) tipo {tipo} en la línea NPS {nps}, conforme a la norma MSS SP-58 y el estándar Repsol ED-L-06.00-05a.</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>tipo, nps</t>
+          <t>cantidad, tipo, nps</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>tipo=U-bolt</t>
+          <t>cantidad=varias</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3071,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>union bridada | uniones bridadas | unión bridada | uniones bridada</t>
+          <t>union bridada | uniones bridadas | unión bridada | uniones bridada | brida | bridas | niple | niples</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2897,6 +2897,43 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_CHAQUETA_METALICA_AUSENTE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ausencia de chaqueta metálica (sin afectar el material aislante)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ausencia de chaqueta metálica (cubierta protectora) en {cantidad} sector(es)/tramo(s) de {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros), sin afectar el material aislante.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Instalar la chaqueta metálica (cubierta protectora) faltante en {cantidad} sector(es)/tramo(s) de {ubicacion} de NPS {nps} (longitud aprox. {longitud} metros), para proteger el material aislante existente, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>cantidad, ubicacion, nps, longitud</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>cantidad=varios</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2909,7 +2946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3966,7 +4003,11 @@
           <t>aislamiento</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>chaqueta metalica | chaqueta metálica | cubierta protectora</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -6163,6 +6204,52 @@
       <c r="E135" t="inlineStr">
         <is>
           <t>humedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>66</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_CHAQUETA_METALICA_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>ausencia | ausente</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>66</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_CHAQUETA_METALICA_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>aislamiento</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>chaqueta metalica | chaqueta metálica | cubierta protectora | cubierta metalica | cubierta metálica</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1456,20 +1456,24 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Abertura(s) en la cubierta metálica, abolladuras, deterioro y/o exposición del material aislante en {ubicacion} del circuito NPS {nps}.</t>
+          <t>Se evidencia {cantidad} abertura(s) en la cubierta metálica, abolladuras, deterioro y/o exposición del material aislante en {ubicacion} del circuito NPS {nps}.</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Reparar el aislamiento térmico en {ubicacion} del circuito NPS {nps}, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
+          <t>Reparar el aislamiento térmico en {cantidad} zona(s) de {ubicacion} del circuito NPS {nps}, siguiendo los lineamientos del API 583 sección 9.6.a, del estándar Repsol ED-N-01.00-03 y del documento PE-N-0100.01.</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>ubicacion, nps</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
+          <t>cantidad, ubicacion, nps</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -3008,7 +3012,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento</t>
+          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento | perdida total de recubrimiento | pérdida total de recubrimiento | perdida total del recubrimiento | pérdida total del recubrimiento | perdida de recubrimiento | pérdida de recubrimiento | perdida del recubrimiento | pérdida del recubrimiento</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr"/>
@@ -4391,7 +4395,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento</t>
+          <t>deterioro del recubrimiento | deterioro recubrimiento | deterioro del recubirmiento | perdida total de recubrimiento | pérdida total de recubrimiento | perdida total del recubrimiento | pérdida total del recubrimiento | perdida de recubrimiento | pérdida de recubrimiento | perdida del recubrimiento | pérdida del recubrimiento</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2938,6 +2938,43 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BRIDA_CIEGA_AUSENTE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ausencia de brida ciega en conexión bridada</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ausencia de brida ciega en {cantidad} conexión(es) bridada(s) de NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Realizar la instalación de {cantidad} brida(s) ciega(s) de NPS {nps} en la conexión bridada correspondiente, conforme a los procedimientos de mantenimiento Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>cantidad, nps</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,7 +2987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6257,6 +6294,52 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>67</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BRIDA_CIEGA_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>brida ciega | bridas ciegas | brida ciega faltante</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>67</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BRIDA_CIEGA_AUSENTE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>bridas</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ausencia | ausente | falta de | sin brida ciega | no cuenta con</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} unión(es) bridada(s) de NPS {nps}, incluyendo sus elementos de ajuste (tuercas y espárragos), conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
+          <t>Realizar limpieza mecánica, mantenimiento del recubrimiento y aplicar lubricante tipo Molykote 1000 en {cantidad} unión(es) bridada(s) de NPS {nps}, incluyendo elementos de ajuste, conforme al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006 (Secc. 3.4.2) y los estándares Repsol ED-B-06.00-04d y PE-B-0600.01H00R05.</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, empleando el WPS y PQR correspondientes, debidamente calificados.</t>
+          <t>Aplicar soldadura de sello en las conexiones de las líneas de toma raíz con la brida de orificio {tag}, con WPS y PQR calificados.</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento preventivo de la válvula de drenaje de NPS {nps} y de la unión roscada entre el tapón y el niple, incluyendo pruebas de apertura y cierre para asegurar su correcto funcionamiento y un sello eficaz, conforme al estándar API 570, sección 7.12.</t>
+          <t>Realizar el mantenimiento correctivo de la válvula de drenaje de NPS {nps} y de la unión roscada entre el tapón y el niple, incluyendo pruebas de apertura y cierre para asegurar su correcto funcionamiento y un sello eficaz, conforme al estándar API 570, sección 7.12.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Realizar el mantenimiento o el reemplazo del bulón de anclaje del soporte cerca de {ubicacion}, conforme a los procedimientos y estándares Repsol aplicables.</t>
+          <t>Realizar el mantenimiento del bulón de anclaje del soporte cerca de {ubicacion}, conforme a los procedimientos y estándares Repsol aplicables.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>severidad=moderada a severa</t>
+          <t>severidad=leve a moderada</t>
         </is>
       </c>
     </row>
@@ -2972,6 +2972,107 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>cantidad=varias</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Corrosión severa en soporte metálico (reemplazo)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Deterioro del recubrimiento y corrosión severa en el soporte tipo {tipo} de la línea NPS {nps}.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo del soporte tipo {tipo} de la línea NPS {nps}, siguiendo los estándares Repsol ED-B-06.00-04d, PE-B-0600.01H00R05 y ED-L-06.00-05a (sección 5.5) y la norma MSS SP-58.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>tipo, nps</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BRIDA_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BRIDA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Corrosión severa en brida (reemplazo)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hallazgo: Presencia de corrosión severa en {cantidad} unión(es) bridada(s) de NPS {nps}, con pérdida de material en la brida.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo de {cantidad} brida(s) de NPS {nps} afectada(s) por la corrosión, conforme a ASME B31.3 y al procedimiento Repsol RLP-FM-MANT-PRO-06-01.006.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>cantidad, nps</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>cantidad=varias</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Corrosión severa en bulón de anclaje (reemplazo)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Corrosión severa en el bulón de anclaje del soporte cerca de {ubicacion}.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Realizar el reemplazo del bulón de anclaje del soporte cerca de {ubicacion}, conforme a los procedimientos y estándares Repsol aplicables.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
         </is>
       </c>
     </row>
@@ -2987,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6340,6 +6441,228 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>56</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>leve | moderada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>68</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>corrosion | corrosión</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>68</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>68</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SOPORTE_METALICO_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>soportes; abrazaderas</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>soporte</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>spring hanger | u-bolt | u bolt | ubolt | bulon de anclaje | bulón de anclaje | abrazadera</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>69</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BRIDA_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>bridas; placas orificio</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>corrosion | corrosión</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>69</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BRIDA_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>bridas; placas orificio</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>69</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BRIDA_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bridas; placas orificio</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>3</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>union bridada | uniones bridadas | unión bridada | uniones bridada | brida | bridas</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>galvan | gálvan | esparrago | espárrago | esparragos | espárragos | perno | pernos</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>70</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>bulon de anclaje | bulón de anclaje | perno de anclaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>70</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SOPORTE_BULON_ANCLAJE_CORROSION_SEVERA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>soportes</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>severa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -881,12 +881,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Circuito NPS {nps} evidencia corrosión en zonas sin acceso para inspección visual adecuada, por encontrarse en altura.</t>
+          <t>Presencia de corrosión (otros) en tramo no accesible de la línea NPS {nps}, cerca de {ubicacion}, por encontrarse en altura, lo que no permite calificar su severidad mediante inspección visual (VT).</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Se requiere instalar facilidades (andamios de {longitud} metros) para acceder a la zona cerca de {ubicacion} y complementar la inspección de la zona observada en la tubería de NPS {nps}.</t>
+          <t>Instalar facilidades de acceso (andamios de {longitud} metros) cerca de {ubicacion} para realizar la inspección visual (VT) adecuada de la línea NPS {nps} y determinar el grado de corrosión (daño) real.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">

--- a/Catalogo_Hallazgos_Recomendaciones.xlsx
+++ b/Catalogo_Hallazgos_Recomendaciones.xlsx
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Se evidencia falta de paralelismo en el montaje de la unión bridada de NPS {nps}.</t>
+          <t>Desviación de paralelismo entre caras de brida en unión bridada de NPS {nps}, con una separación de {separacion}.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>nps</t>
+          <t>nps, separacion</t>
         </is>
       </c>
     </row>
